--- a/database/register/BIOLOOP_streams_and_sources.xlsx
+++ b/database/register/BIOLOOP_streams_and_sources.xlsx
@@ -12,14 +12,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$C$1:$V$92</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.#####"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +52,21 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <color rgb="FF1E241D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF5A6357"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -85,11 +100,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -123,12 +150,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -171,6 +207,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -542,10 +592,10 @@
   <cols>
     <col width="7.26953125" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="51.6328125" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="81.54296875" customWidth="1" min="4" max="4"/>
+    <col width="30.81640625" customWidth="1" min="5" max="5"/>
     <col width="22.6328125" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="38.1796875" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -769,7 +819,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S2" s="14" t="n">
+      <c r="S2" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T2" s="14" t="inlineStr">
@@ -875,7 +925,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S3" s="14" t="n">
+      <c r="S3" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T3" s="14" t="inlineStr">
@@ -981,7 +1031,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S4" s="14" t="n">
+      <c r="S4" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="14" t="inlineStr">
@@ -1087,7 +1137,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S5" s="14" t="n">
+      <c r="S5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T5" s="14" t="inlineStr">
@@ -1196,7 +1246,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,7 +1348,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -1405,7 +1455,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
@@ -1507,7 +1557,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
@@ -1614,7 +1664,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
@@ -1721,7 +1771,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
@@ -1828,7 +1878,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
@@ -1935,7 +1985,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
@@ -2042,7 +2092,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
@@ -2149,7 +2199,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
@@ -2256,7 +2306,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
@@ -2363,7 +2413,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
@@ -2470,7 +2520,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
@@ -2577,7 +2627,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
@@ -2684,7 +2734,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
@@ -2791,7 +2841,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
@@ -2898,7 +2948,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
@@ -3005,7 +3055,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
@@ -3112,7 +3162,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
@@ -3219,7 +3269,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
@@ -3326,7 +3376,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
@@ -3433,7 +3483,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
@@ -3540,7 +3590,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
@@ -3647,7 +3697,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
@@ -3754,7 +3804,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
@@ -3861,7 +3911,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
@@ -3968,7 +4018,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="S32" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
@@ -4075,7 +4125,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
@@ -4182,7 +4232,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
@@ -4289,7 +4339,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="S35" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
@@ -4391,7 +4441,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
@@ -4493,7 +4543,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="S37" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
@@ -4595,7 +4645,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="S38" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
@@ -4697,7 +4747,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="S39" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
@@ -4794,7 +4844,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
@@ -4896,7 +4946,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="S41" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
@@ -5003,7 +5053,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="S42" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
@@ -5110,7 +5160,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="S43" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
@@ -5217,7 +5267,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="S44" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
@@ -5314,7 +5364,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="S45" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
@@ -5411,7 +5461,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="S46" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
@@ -5513,7 +5563,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="S47" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
@@ -5615,7 +5665,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="S48" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
@@ -5712,7 +5762,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="S49" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
@@ -5812,7 +5862,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S50" s="14" t="n">
+      <c r="S50" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="14" t="inlineStr">
@@ -5918,7 +5968,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S51" s="14" t="n">
+      <c r="S51" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="14" t="inlineStr">
@@ -6022,7 +6072,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="S52" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
@@ -6124,7 +6174,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="S53" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
@@ -6226,7 +6276,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="S54" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
@@ -6323,7 +6373,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="S55" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
@@ -6425,7 +6475,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="S56" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
@@ -6532,7 +6582,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="S57" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
@@ -6639,7 +6689,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="S58" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
@@ -6736,7 +6786,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="S59" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
@@ -6838,7 +6888,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="S60" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
@@ -6940,7 +6990,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="S61" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
@@ -7037,7 +7087,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S62" t="n">
+      <c r="S62" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
@@ -7139,7 +7189,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="S63" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
@@ -7241,7 +7291,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S64" t="n">
+      <c r="S64" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
@@ -7343,7 +7393,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S65" t="n">
+      <c r="S65" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
@@ -7440,7 +7490,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="S66" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
@@ -7542,7 +7592,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S67" t="n">
+      <c r="S67" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
@@ -7649,7 +7699,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="S68" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
@@ -7756,7 +7806,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S69" t="n">
+      <c r="S69" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
@@ -7853,7 +7903,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="S70" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
@@ -7955,7 +8005,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="S71" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
@@ -8057,7 +8107,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="S72" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
@@ -8154,7 +8204,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S73" t="n">
+      <c r="S73" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
@@ -8254,7 +8304,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S74" s="14" t="n">
+      <c r="S74" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T74" s="14" t="inlineStr">
@@ -8360,7 +8410,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S75" s="14" t="n">
+      <c r="S75" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T75" s="14" t="inlineStr">
@@ -8470,7 +8520,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S76" s="14" t="n">
+      <c r="S76" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T76" s="14" t="inlineStr">
@@ -8576,7 +8626,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S77" s="14" t="n">
+      <c r="S77" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T77" s="14" t="inlineStr">
@@ -8682,7 +8732,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S78" s="14" t="n">
+      <c r="S78" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T78" s="14" t="inlineStr">
@@ -8795,7 +8845,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S79" t="n">
+      <c r="S79" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
@@ -8902,7 +8952,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S80" t="n">
+      <c r="S80" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
@@ -9009,7 +9059,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S81" t="n">
+      <c r="S81" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
@@ -9116,7 +9166,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S82" t="n">
+      <c r="S82" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
@@ -9223,7 +9273,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S83" t="n">
+      <c r="S83" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
@@ -9330,7 +9380,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S84" t="n">
+      <c r="S84" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
@@ -9437,7 +9487,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S85" t="n">
+      <c r="S85" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
@@ -9544,7 +9594,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S86" t="n">
+      <c r="S86" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
@@ -9641,7 +9691,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="S87" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
@@ -9738,7 +9788,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S88" t="n">
+      <c r="S88" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
@@ -9840,7 +9890,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S89" t="n">
+      <c r="S89" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
@@ -9942,7 +9992,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S90" t="n">
+      <c r="S90" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T90" t="inlineStr">
@@ -10047,7 +10097,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S91" s="14" t="n">
+      <c r="S91" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T91" s="14" t="inlineStr">
@@ -10153,7 +10203,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S92" s="14" t="n">
+      <c r="S92" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T92" s="14" t="inlineStr">
@@ -10259,7 +10309,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S93" s="14" t="n">
+      <c r="S93" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T93" s="14" t="inlineStr">
@@ -10362,7 +10412,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S94" t="n">
+      <c r="S94" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
@@ -10459,7 +10509,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S95" t="n">
+      <c r="S95" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
@@ -10556,7 +10606,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S96" t="n">
+      <c r="S96" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
@@ -10653,7 +10703,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S97" t="n">
+      <c r="S97" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T97" t="inlineStr">
@@ -10750,7 +10800,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S98" t="n">
+      <c r="S98" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
@@ -10847,7 +10897,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S99" t="n">
+      <c r="S99" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
@@ -10944,7 +10994,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S100" t="n">
+      <c r="S100" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T100" t="inlineStr">
@@ -11046,7 +11096,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S101" t="n">
+      <c r="S101" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
@@ -11146,7 +11196,7 @@
           <t>miljoen ton</t>
         </is>
       </c>
-      <c r="S102" s="14" t="n">
+      <c r="S102" s="23" t="n">
         <v>1000000</v>
       </c>
       <c r="T102" s="14" t="inlineStr">
@@ -11250,7 +11300,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S103" t="n">
+      <c r="S103" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
@@ -11347,7 +11397,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="S104" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
@@ -11444,7 +11494,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S105" t="n">
+      <c r="S105" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
@@ -11544,7 +11594,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S106" s="14" t="n">
+      <c r="S106" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T106" s="14" t="inlineStr">
@@ -11647,7 +11697,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S107" t="n">
+      <c r="S107" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
@@ -11744,7 +11794,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S108" t="n">
+      <c r="S108" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
@@ -11844,7 +11894,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S109" s="14" t="n">
+      <c r="S109" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T109" s="14" t="inlineStr">
@@ -11950,7 +12000,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S110" s="14" t="n">
+      <c r="S110" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T110" s="14" t="inlineStr">
@@ -12056,7 +12106,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S111" s="14" t="n">
+      <c r="S111" s="23" t="n">
         <v>1</v>
       </c>
       <c r="T111" s="14" t="inlineStr">
@@ -12120,9 +12170,9 @@
           <t>Aggregaat</t>
         </is>
       </c>
-      <c r="G112" s="15" t="inlineStr"/>
-      <c r="H112" s="15" t="inlineStr"/>
-      <c r="I112" s="15" t="inlineStr"/>
+      <c r="G112" s="15" t="n"/>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="15" t="n"/>
       <c r="J112" s="15" t="n">
         <v>2</v>
       </c>
@@ -12162,7 +12212,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S112" s="15" t="n">
+      <c r="S112" s="25" t="n">
         <v>1</v>
       </c>
       <c r="T112" s="15" t="inlineStr">
@@ -12190,7 +12240,7 @@
           <t>read in PDF</t>
         </is>
       </c>
-      <c r="Y112" s="15" t="inlineStr"/>
+      <c r="Y112" s="15" t="n"/>
       <c r="Z112" s="15" t="n"/>
     </row>
     <row r="113">
@@ -12222,9 +12272,9 @@
           <t>Aggregaat</t>
         </is>
       </c>
-      <c r="G113" s="15" t="inlineStr"/>
-      <c r="H113" s="15" t="inlineStr"/>
-      <c r="I113" s="15" t="inlineStr"/>
+      <c r="G113" s="15" t="n"/>
+      <c r="H113" s="15" t="n"/>
+      <c r="I113" s="15" t="n"/>
       <c r="J113" s="15" t="n">
         <v>2</v>
       </c>
@@ -12264,7 +12314,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S113" s="15" t="n">
+      <c r="S113" s="25" t="n">
         <v>1</v>
       </c>
       <c r="T113" s="15" t="inlineStr">
@@ -12292,7 +12342,7 @@
           <t>read in PDF</t>
         </is>
       </c>
-      <c r="Y113" s="15" t="inlineStr"/>
+      <c r="Y113" s="15" t="n"/>
       <c r="Z113" s="15" t="n"/>
     </row>
     <row r="114">
@@ -12324,9 +12374,9 @@
           <t>Aggregaat</t>
         </is>
       </c>
-      <c r="G114" s="15" t="inlineStr"/>
-      <c r="H114" s="15" t="inlineStr"/>
-      <c r="I114" s="15" t="inlineStr"/>
+      <c r="G114" s="15" t="n"/>
+      <c r="H114" s="15" t="n"/>
+      <c r="I114" s="15" t="n"/>
       <c r="J114" s="15" t="n">
         <v>2</v>
       </c>
@@ -12366,7 +12416,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S114" s="15" t="n">
+      <c r="S114" s="25" t="n">
         <v>1</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
@@ -12394,110 +12444,110 @@
           <t>read in PDF</t>
         </is>
       </c>
-      <c r="Y114" s="15" t="inlineStr"/>
+      <c r="Y114" s="15" t="n"/>
       <c r="Z114" s="15" t="n"/>
     </row>
-    <row r="115">
-      <c r="A115" s="15" t="n">
+    <row r="115" customFormat="1" s="17">
+      <c r="A115" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="B115" s="16" t="inlineStr">
         <is>
           <t>Tabel 7</t>
         </is>
       </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="C115" s="16" t="inlineStr">
         <is>
           <t>C-114</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
         <is>
           <t>AGGREGAAT - nevenstromen primaire sector (andere bestemming)</t>
         </is>
       </c>
-      <c r="E115" s="15" t="inlineStr">
+      <c r="E115" s="16" t="inlineStr">
         <is>
           <t>Reststroom</t>
         </is>
       </c>
-      <c r="F115" s="15" t="inlineStr">
+      <c r="F115" s="16" t="inlineStr">
         <is>
           <t>Aggregaat</t>
         </is>
       </c>
-      <c r="G115" s="15" t="inlineStr"/>
-      <c r="H115" s="15" t="inlineStr"/>
-      <c r="I115" s="15" t="inlineStr"/>
-      <c r="J115" s="15" t="n">
+      <c r="G115" s="16" t="n"/>
+      <c r="H115" s="16" t="n"/>
+      <c r="I115" s="16" t="n"/>
+      <c r="J115" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="K115" s="15" t="inlineStr">
+      <c r="K115" s="16" t="inlineStr">
         <is>
           <t>primaire sector (visveilingen, landbouwsector, PO's groenten en fruit)</t>
         </is>
       </c>
-      <c r="L115" s="15" t="inlineStr">
+      <c r="L115" s="16" t="inlineStr">
         <is>
           <t>meerdere stadia</t>
         </is>
       </c>
-      <c r="M115" s="15" t="inlineStr">
+      <c r="M115" s="16" t="inlineStr">
         <is>
           <t>S080</t>
         </is>
       </c>
-      <c r="N115" s="15" t="inlineStr">
+      <c r="N115" s="16" t="inlineStr">
         <is>
           <t>OVAM Monitor voedselverlies 2023</t>
         </is>
       </c>
-      <c r="O115" s="15" t="inlineStr">
+      <c r="O115" s="16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="P115" s="15" t="n">
+      <c r="P115" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="Q115" s="15" t="n">
+      <c r="Q115" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="R115" s="15" t="inlineStr">
+      <c r="R115" s="16" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="S115" s="15" t="n">
+      <c r="S115" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T115" s="15" t="inlineStr">
+      <c r="T115" s="16" t="inlineStr">
         <is>
           <t>nevenstroom</t>
         </is>
       </c>
-      <c r="U115" s="15" t="inlineStr">
+      <c r="U115" s="16" t="inlineStr">
         <is>
           <t>voedselverliezen en nevenstromen per schakel in de primaire sector; de bron drukt geen rijtotaal, alleen de opsplitsing ingezameld/andere - nooit optellen met de zusterrij</t>
         </is>
       </c>
-      <c r="V115" s="15" t="inlineStr">
+      <c r="V115" s="16" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="W115" s="15" t="inlineStr">
+      <c r="W115" s="16" t="inlineStr">
         <is>
           <t>Vlaanderen</t>
         </is>
       </c>
-      <c r="X115" s="15" t="inlineStr">
+      <c r="X115" s="16" t="inlineStr">
         <is>
           <t>read in PDF</t>
         </is>
       </c>
-      <c r="Y115" s="15" t="inlineStr"/>
-      <c r="Z115" s="15" t="n"/>
+      <c r="Y115" s="16" t="n"/>
+      <c r="Z115" s="16" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12577,7 +12627,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S116" t="n">
+      <c r="S116" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
@@ -12684,7 +12734,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S117" t="n">
+      <c r="S117" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
@@ -12791,7 +12841,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S118" t="n">
+      <c r="S118" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
@@ -12898,7 +12948,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S119" t="n">
+      <c r="S119" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
@@ -13005,7 +13055,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S120" t="n">
+      <c r="S120" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
@@ -13112,7 +13162,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S121" t="n">
+      <c r="S121" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
@@ -13219,7 +13269,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S122" t="n">
+      <c r="S122" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
@@ -13326,7 +13376,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S123" t="n">
+      <c r="S123" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
@@ -13433,7 +13483,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S124" t="n">
+      <c r="S124" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T124" t="inlineStr">
@@ -13540,7 +13590,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S125" t="n">
+      <c r="S125" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T125" t="inlineStr">
@@ -13647,7 +13697,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S126" t="n">
+      <c r="S126" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
@@ -13754,7 +13804,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S127" t="n">
+      <c r="S127" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T127" t="inlineStr">
@@ -13861,7 +13911,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S128" t="n">
+      <c r="S128" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
@@ -13968,7 +14018,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S129" t="n">
+      <c r="S129" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
@@ -14070,7 +14120,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S130" t="n">
+      <c r="S130" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T130" t="inlineStr">
@@ -14177,7 +14227,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S131" t="n">
+      <c r="S131" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T131" t="inlineStr">
@@ -14284,7 +14334,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S132" t="n">
+      <c r="S132" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
@@ -14391,7 +14441,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S133" t="n">
+      <c r="S133" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
@@ -14498,7 +14548,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S134" t="n">
+      <c r="S134" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
@@ -14605,7 +14655,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S135" t="n">
+      <c r="S135" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T135" t="inlineStr">
@@ -14712,7 +14762,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S136" t="n">
+      <c r="S136" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
@@ -14819,7 +14869,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S137" t="n">
+      <c r="S137" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
@@ -14926,7 +14976,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S138" t="n">
+      <c r="S138" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T138" t="inlineStr">
@@ -15033,7 +15083,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S139" t="n">
+      <c r="S139" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T139" t="inlineStr">
@@ -15140,7 +15190,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S140" t="n">
+      <c r="S140" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
@@ -15247,7 +15297,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S141" t="n">
+      <c r="S141" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
@@ -15354,7 +15404,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S142" t="n">
+      <c r="S142" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T142" t="inlineStr">
@@ -15461,7 +15511,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S143" t="n">
+      <c r="S143" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T143" t="inlineStr">
@@ -15568,7 +15618,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S144" t="n">
+      <c r="S144" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
@@ -15670,7 +15720,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S145" t="n">
+      <c r="S145" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T145" t="inlineStr">
@@ -15777,7 +15827,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S146" t="n">
+      <c r="S146" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T146" t="inlineStr">
@@ -15884,7 +15934,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S147" t="n">
+      <c r="S147" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
@@ -15991,7 +16041,7 @@
           <t>miljoen kg</t>
         </is>
       </c>
-      <c r="S148" t="n">
+      <c r="S148" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T148" t="inlineStr">
@@ -16017,6 +16067,11 @@
       <c r="X148" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16148,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S149" t="n">
+      <c r="S149" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T149" t="inlineStr">
@@ -16119,6 +16174,11 @@
       <c r="X149" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
@@ -16200,7 +16260,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S150" t="n">
+      <c r="S150" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T150" t="inlineStr">
@@ -16302,7 +16362,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S151" t="n">
+      <c r="S151" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T151" t="inlineStr">
@@ -16404,7 +16464,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S152" t="n">
+      <c r="S152" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T152" t="inlineStr">
@@ -16501,7 +16561,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S153" t="n">
+      <c r="S153" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T153" t="inlineStr">
@@ -16608,7 +16668,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S154" t="n">
+      <c r="S154" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T154" t="inlineStr">
@@ -16715,7 +16775,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S155" t="n">
+      <c r="S155" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T155" t="inlineStr">
@@ -16822,7 +16882,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S156" t="n">
+      <c r="S156" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T156" t="inlineStr">
@@ -16919,7 +16979,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S157" t="n">
+      <c r="S157" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T157" t="inlineStr">
@@ -17026,7 +17086,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S158" t="n">
+      <c r="S158" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T158" t="inlineStr">
@@ -17128,7 +17188,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S159" t="n">
+      <c r="S159" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T159" t="inlineStr">
@@ -17225,7 +17285,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S160" t="n">
+      <c r="S160" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T160" t="inlineStr">
@@ -17327,7 +17387,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S161" t="n">
+      <c r="S161" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T161" t="inlineStr">
@@ -17434,7 +17494,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S162" t="n">
+      <c r="S162" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T162" t="inlineStr">
@@ -17536,7 +17596,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S163" t="n">
+      <c r="S163" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T163" t="inlineStr">
@@ -17638,7 +17698,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S164" t="n">
+      <c r="S164" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T164" t="inlineStr">
@@ -17735,7 +17795,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S165" t="n">
+      <c r="S165" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T165" t="inlineStr">
@@ -17837,7 +17897,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S166" t="n">
+      <c r="S166" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T166" t="inlineStr">
@@ -17944,7 +18004,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S167" t="n">
+      <c r="S167" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T167" t="inlineStr">
@@ -18051,7 +18111,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S168" t="n">
+      <c r="S168" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T168" t="inlineStr">
@@ -18148,7 +18208,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S169" t="n">
+      <c r="S169" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T169" t="inlineStr">
@@ -18250,7 +18310,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S170" t="n">
+      <c r="S170" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T170" t="inlineStr">
@@ -18352,7 +18412,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S171" t="n">
+      <c r="S171" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T171" t="inlineStr">
@@ -18449,7 +18509,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S172" t="n">
+      <c r="S172" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T172" t="inlineStr">
@@ -18546,7 +18606,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S173" t="n">
+      <c r="S173" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T173" t="inlineStr">
@@ -18653,7 +18713,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S174" t="n">
+      <c r="S174" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T174" t="inlineStr">
@@ -18755,7 +18815,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S175" t="n">
+      <c r="S175" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T175" t="inlineStr">
@@ -18857,7 +18917,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S176" t="n">
+      <c r="S176" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T176" t="inlineStr">
@@ -18954,7 +19014,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S177" t="n">
+      <c r="S177" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T177" t="inlineStr">
@@ -19056,7 +19116,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S178" t="n">
+      <c r="S178" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T178" t="inlineStr">
@@ -19163,7 +19223,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S179" t="n">
+      <c r="S179" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T179" t="inlineStr">
@@ -19270,7 +19330,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S180" t="n">
+      <c r="S180" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T180" t="inlineStr">
@@ -19367,7 +19427,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S181" t="n">
+      <c r="S181" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T181" t="inlineStr">
@@ -19469,7 +19529,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S182" t="n">
+      <c r="S182" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T182" t="inlineStr">
@@ -19571,7 +19631,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S183" t="n">
+      <c r="S183" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T183" t="inlineStr">
@@ -19668,7 +19728,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S184" t="n">
+      <c r="S184" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T184" t="inlineStr">
@@ -19765,7 +19825,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S185" t="n">
+      <c r="S185" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T185" t="inlineStr">
@@ -19867,7 +19927,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S186" t="n">
+      <c r="S186" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T186" t="inlineStr">
@@ -19893,6 +19953,11 @@
       <c r="X186" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
@@ -19969,7 +20034,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S187" t="n">
+      <c r="S187" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T187" t="inlineStr">
@@ -20071,7 +20136,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S188" t="n">
+      <c r="S188" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T188" t="inlineStr">
@@ -20173,7 +20238,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S189" t="n">
+      <c r="S189" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T189" t="inlineStr">
@@ -20275,7 +20340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S190" t="n">
+      <c r="S190" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T190" t="inlineStr">
@@ -20377,7 +20442,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S191" t="n">
+      <c r="S191" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
@@ -20479,7 +20544,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S192" t="n">
+      <c r="S192" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T192" t="inlineStr">
@@ -20581,7 +20646,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S193" t="n">
+      <c r="S193" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T193" t="inlineStr">
@@ -20683,7 +20748,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S194" t="n">
+      <c r="S194" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T194" t="inlineStr">
@@ -20709,6 +20774,11 @@
       <c r="X194" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
@@ -20785,7 +20855,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S195" t="n">
+      <c r="S195" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T195" t="inlineStr">
@@ -20882,7 +20952,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S196" t="n">
+      <c r="S196" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T196" t="inlineStr">
@@ -20979,7 +21049,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S197" t="n">
+      <c r="S197" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T197" t="inlineStr">
@@ -21076,7 +21146,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S198" t="n">
+      <c r="S198" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T198" t="inlineStr">
@@ -21173,7 +21243,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S199" t="n">
+      <c r="S199" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T199" t="inlineStr">
@@ -21270,7 +21340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S200" t="n">
+      <c r="S200" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T200" t="inlineStr">
@@ -21372,7 +21442,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S201" t="n">
+      <c r="S201" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T201" t="inlineStr">
@@ -21469,7 +21539,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S202" t="n">
+      <c r="S202" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T202" t="inlineStr">
@@ -21566,7 +21636,7 @@
           <t>miljoen ton</t>
         </is>
       </c>
-      <c r="S203" t="n">
+      <c r="S203" s="24" t="n">
         <v>1000000</v>
       </c>
       <c r="T203" t="inlineStr">
@@ -21663,7 +21733,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S204" t="n">
+      <c r="S204" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T204" t="inlineStr">
@@ -21765,7 +21835,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S205" t="n">
+      <c r="S205" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T205" t="inlineStr">
@@ -21867,7 +21937,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S206" t="n">
+      <c r="S206" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T206" t="inlineStr">
@@ -21969,7 +22039,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S207" t="n">
+      <c r="S207" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T207" t="inlineStr">
@@ -22071,7 +22141,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S208" t="n">
+      <c r="S208" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T208" t="inlineStr">
@@ -22173,7 +22243,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S209" t="n">
+      <c r="S209" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T209" t="inlineStr">
@@ -22270,7 +22340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S210" t="n">
+      <c r="S210" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T210" t="inlineStr">
@@ -22367,7 +22437,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S211" t="n">
+      <c r="S211" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T211" t="inlineStr">
@@ -22464,7 +22534,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S212" t="n">
+      <c r="S212" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T212" t="inlineStr">
@@ -22561,7 +22631,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S213" t="n">
+      <c r="S213" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
@@ -22658,7 +22728,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S214" t="n">
+      <c r="S214" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
@@ -22687,98 +22757,98 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="n">
+    <row r="215" customFormat="1" s="17">
+      <c r="A215" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="17" t="inlineStr">
         <is>
           <t>Tabel 10</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="17" t="inlineStr">
         <is>
           <t>C-214</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="17" t="inlineStr">
         <is>
           <t>AGGREGAAT - levensmiddelenafval retail (EU-definitie voedselafval)</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="17" t="inlineStr">
         <is>
           <t>Reststroom</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" s="17" t="inlineStr">
         <is>
           <t>Aggregaat</t>
         </is>
       </c>
-      <c r="J215" t="n">
+      <c r="J215" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="K215" s="17" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="L215" s="17" t="inlineStr">
         <is>
           <t>Retail &amp; grootdistributie</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
+      <c r="M215" s="17" t="inlineStr">
         <is>
           <t>S002</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr">
+      <c r="N215" s="17" t="inlineStr">
         <is>
           <t>OVAM Monitor voedselverlies 2020</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="O215" s="17" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="P215" t="n">
+      <c r="P215" s="17" t="n">
         <v>65782</v>
       </c>
-      <c r="Q215" t="n">
+      <c r="Q215" s="17" t="n">
         <v>65782</v>
       </c>
-      <c r="R215" t="inlineStr">
+      <c r="R215" s="17" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="S215" t="n">
+      <c r="S215" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="T215" t="inlineStr">
+      <c r="T215" s="17" t="inlineStr">
         <is>
           <t>agri-food waste</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="U215" s="17" t="inlineStr">
         <is>
           <t>voedselafval volgens de Europese afbakening (specifieke Eural-codes; enkel de bestemmingen compostering/vergisting, dierlijke afvalverwerking en verbranding) - parallelle boekhouding naast de Vlaamse cijfers</t>
         </is>
       </c>
-      <c r="V215" t="inlineStr">
+      <c r="V215" s="17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W215" t="inlineStr">
+      <c r="W215" s="17" t="inlineStr">
         <is>
           <t>Vlaanderen</t>
         </is>
       </c>
-      <c r="X215" t="inlineStr">
+      <c r="X215" s="17" t="inlineStr">
         <is>
           <t>read in PDF</t>
         </is>
@@ -22795,7 +22865,7 @@
           <t>Tabel 13</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" s="19" t="inlineStr">
         <is>
           <t>C-215</t>
         </is>
@@ -22854,7 +22924,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S216" t="n">
+      <c r="S216" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T216" t="inlineStr">
@@ -22899,7 +22969,7 @@
           <t>Tabel 13</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="19" t="inlineStr">
         <is>
           <t>C-216</t>
         </is>
@@ -22958,7 +23028,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S217" t="n">
+      <c r="S217" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T217" t="inlineStr">
@@ -23003,7 +23073,7 @@
           <t>Tabel 13</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="19" t="inlineStr">
         <is>
           <t>C-217</t>
         </is>
@@ -23062,7 +23132,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S218" t="n">
+      <c r="S218" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T218" t="inlineStr">
@@ -23102,7 +23172,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="19" t="inlineStr">
         <is>
           <t>C-218</t>
         </is>
@@ -23161,7 +23231,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S219" t="n">
+      <c r="S219" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T219" t="inlineStr">
@@ -23171,7 +23241,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>hoofdstromen uit de landbouwteelten</t>
+          <t>hoofdstromen uit de landbouwteelten; LET OP: dit totaal OMVAT de sierteelt, die als niet-agrovoeding niet apart gecapteerd is, zodat de gecapteerde gewasgroeprijen niet tot dit totaal sommeren</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
@@ -23206,7 +23276,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="19" t="inlineStr">
         <is>
           <t>C-219</t>
         </is>
@@ -23270,7 +23340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S220" t="n">
+      <c r="S220" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T220" t="inlineStr">
@@ -23310,7 +23380,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="19" t="inlineStr">
         <is>
           <t>C-220</t>
         </is>
@@ -23374,7 +23444,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S221" t="n">
+      <c r="S221" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T221" t="inlineStr">
@@ -23414,7 +23484,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="19" t="inlineStr">
         <is>
           <t>C-221</t>
         </is>
@@ -23478,7 +23548,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S222" t="n">
+      <c r="S222" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T222" t="inlineStr">
@@ -23518,7 +23588,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="19" t="inlineStr">
         <is>
           <t>C-222</t>
         </is>
@@ -23582,7 +23652,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S223" t="n">
+      <c r="S223" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T223" t="inlineStr">
@@ -23622,7 +23692,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="19" t="inlineStr">
         <is>
           <t>C-223</t>
         </is>
@@ -23686,7 +23756,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S224" t="n">
+      <c r="S224" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T224" t="inlineStr">
@@ -23726,7 +23796,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="19" t="inlineStr">
         <is>
           <t>C-224</t>
         </is>
@@ -23790,7 +23860,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S225" t="n">
+      <c r="S225" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T225" t="inlineStr">
@@ -23830,7 +23900,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C226" s="19" t="inlineStr">
         <is>
           <t>C-225</t>
         </is>
@@ -23894,7 +23964,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S226" t="n">
+      <c r="S226" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T226" t="inlineStr">
@@ -23934,7 +24004,7 @@
           <t>Figuur 8</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="19" t="inlineStr">
         <is>
           <t>C-226</t>
         </is>
@@ -23998,7 +24068,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S227" t="n">
+      <c r="S227" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T227" t="inlineStr">
@@ -24038,7 +24108,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C228" s="19" t="inlineStr">
         <is>
           <t>C-227</t>
         </is>
@@ -24107,7 +24177,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S228" t="n">
+      <c r="S228" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T228" t="inlineStr">
@@ -24147,7 +24217,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C229" s="19" t="inlineStr">
         <is>
           <t>C-228</t>
         </is>
@@ -24216,7 +24286,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S229" t="n">
+      <c r="S229" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T229" t="inlineStr">
@@ -24256,7 +24326,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C230" s="19" t="inlineStr">
         <is>
           <t>C-229</t>
         </is>
@@ -24325,7 +24395,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S230" t="n">
+      <c r="S230" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T230" t="inlineStr">
@@ -24365,7 +24435,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C231" s="19" t="inlineStr">
         <is>
           <t>C-230</t>
         </is>
@@ -24434,7 +24504,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S231" t="n">
+      <c r="S231" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T231" t="inlineStr">
@@ -24474,7 +24544,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C232" s="19" t="inlineStr">
         <is>
           <t>C-231</t>
         </is>
@@ -24543,7 +24613,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S232" t="n">
+      <c r="S232" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T232" t="inlineStr">
@@ -24583,7 +24653,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="19" t="inlineStr">
         <is>
           <t>C-232</t>
         </is>
@@ -24652,7 +24722,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S233" t="n">
+      <c r="S233" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T233" t="inlineStr">
@@ -24692,7 +24762,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="19" t="inlineStr">
         <is>
           <t>C-233</t>
         </is>
@@ -24761,7 +24831,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S234" t="n">
+      <c r="S234" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T234" t="inlineStr">
@@ -24801,7 +24871,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="19" t="inlineStr">
         <is>
           <t>C-234</t>
         </is>
@@ -24870,7 +24940,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S235" t="n">
+      <c r="S235" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T235" t="inlineStr">
@@ -24910,7 +24980,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="19" t="inlineStr">
         <is>
           <t>C-235</t>
         </is>
@@ -24979,7 +25049,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S236" t="n">
+      <c r="S236" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T236" t="inlineStr">
@@ -25019,7 +25089,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="19" t="inlineStr">
         <is>
           <t>C-236</t>
         </is>
@@ -25088,7 +25158,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S237" t="n">
+      <c r="S237" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T237" t="inlineStr">
@@ -25128,7 +25198,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="19" t="inlineStr">
         <is>
           <t>C-237</t>
         </is>
@@ -25197,7 +25267,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S238" t="n">
+      <c r="S238" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T238" t="inlineStr">
@@ -25237,7 +25307,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="19" t="inlineStr">
         <is>
           <t>C-238</t>
         </is>
@@ -25296,7 +25366,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S239" t="n">
+      <c r="S239" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T239" t="inlineStr">
@@ -25341,7 +25411,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C240" s="19" t="inlineStr">
         <is>
           <t>C-239</t>
         </is>
@@ -25405,7 +25475,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S240" t="n">
+      <c r="S240" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T240" t="inlineStr">
@@ -25445,7 +25515,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="19" t="inlineStr">
         <is>
           <t>C-240</t>
         </is>
@@ -25509,7 +25579,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S241" t="n">
+      <c r="S241" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T241" t="inlineStr">
@@ -25549,7 +25619,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C242" s="19" t="inlineStr">
         <is>
           <t>C-241</t>
         </is>
@@ -25613,7 +25683,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S242" t="n">
+      <c r="S242" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T242" t="inlineStr">
@@ -25653,7 +25723,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C243" s="19" t="inlineStr">
         <is>
           <t>C-242</t>
         </is>
@@ -25717,7 +25787,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S243" t="n">
+      <c r="S243" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T243" t="inlineStr">
@@ -25757,7 +25827,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C244" s="19" t="inlineStr">
         <is>
           <t>C-243</t>
         </is>
@@ -25821,7 +25891,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S244" t="n">
+      <c r="S244" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T244" t="inlineStr">
@@ -25861,7 +25931,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="19" t="inlineStr">
         <is>
           <t>C-244</t>
         </is>
@@ -25925,7 +25995,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S245" t="n">
+      <c r="S245" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T245" t="inlineStr">
@@ -25965,7 +26035,7 @@
           <t>Figuur 14</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="19" t="inlineStr">
         <is>
           <t>C-245</t>
         </is>
@@ -26029,7 +26099,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S246" t="n">
+      <c r="S246" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T246" t="inlineStr">
@@ -26074,7 +26144,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="19" t="inlineStr">
         <is>
           <t>C-246</t>
         </is>
@@ -26148,7 +26218,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S247" t="n">
+      <c r="S247" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T247" t="inlineStr">
@@ -26188,7 +26258,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="19" t="inlineStr">
         <is>
           <t>C-247</t>
         </is>
@@ -26262,7 +26332,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S248" t="n">
+      <c r="S248" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T248" t="inlineStr">
@@ -26302,7 +26372,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="19" t="inlineStr">
         <is>
           <t>C-248</t>
         </is>
@@ -26376,7 +26446,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S249" t="n">
+      <c r="S249" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T249" t="inlineStr">
@@ -26416,7 +26486,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="19" t="inlineStr">
         <is>
           <t>C-249</t>
         </is>
@@ -26490,7 +26560,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S250" t="n">
+      <c r="S250" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T250" t="inlineStr">
@@ -26530,7 +26600,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="19" t="inlineStr">
         <is>
           <t>C-250</t>
         </is>
@@ -26604,7 +26674,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S251" t="n">
+      <c r="S251" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T251" t="inlineStr">
@@ -26644,7 +26714,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="19" t="inlineStr">
         <is>
           <t>C-251</t>
         </is>
@@ -26718,7 +26788,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S252" t="n">
+      <c r="S252" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T252" t="inlineStr">
@@ -26758,7 +26828,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="19" t="inlineStr">
         <is>
           <t>C-252</t>
         </is>
@@ -26832,7 +26902,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S253" t="n">
+      <c r="S253" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T253" t="inlineStr">
@@ -26872,7 +26942,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="19" t="inlineStr">
         <is>
           <t>C-253</t>
         </is>
@@ -26946,7 +27016,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S254" t="n">
+      <c r="S254" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T254" t="inlineStr">
@@ -26986,7 +27056,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="19" t="inlineStr">
         <is>
           <t>C-254</t>
         </is>
@@ -27060,7 +27130,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S255" t="n">
+      <c r="S255" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T255" t="inlineStr">
@@ -27100,7 +27170,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="19" t="inlineStr">
         <is>
           <t>C-255</t>
         </is>
@@ -27174,7 +27244,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S256" t="n">
+      <c r="S256" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T256" t="inlineStr">
@@ -27214,7 +27284,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="19" t="inlineStr">
         <is>
           <t>C-256</t>
         </is>
@@ -27288,7 +27358,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S257" t="n">
+      <c r="S257" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T257" t="inlineStr">
@@ -27333,7 +27403,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="19" t="inlineStr">
         <is>
           <t>C-257</t>
         </is>
@@ -27402,7 +27472,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S258" t="n">
+      <c r="S258" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T258" t="inlineStr">
@@ -27442,7 +27512,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="19" t="inlineStr">
         <is>
           <t>C-258</t>
         </is>
@@ -27511,7 +27581,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S259" t="n">
+      <c r="S259" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T259" t="inlineStr">
@@ -27551,7 +27621,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C260" s="19" t="inlineStr">
         <is>
           <t>C-259</t>
         </is>
@@ -27620,7 +27690,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S260" t="n">
+      <c r="S260" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T260" t="inlineStr">
@@ -27660,7 +27730,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C261" s="19" t="inlineStr">
         <is>
           <t>C-260</t>
         </is>
@@ -27729,7 +27799,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S261" t="n">
+      <c r="S261" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T261" t="inlineStr">
@@ -27769,7 +27839,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="19" t="inlineStr">
         <is>
           <t>C-261</t>
         </is>
@@ -27838,7 +27908,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S262" t="n">
+      <c r="S262" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T262" t="inlineStr">
@@ -27878,7 +27948,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C263" s="19" t="inlineStr">
         <is>
           <t>C-262</t>
         </is>
@@ -27942,7 +28012,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S263" t="n">
+      <c r="S263" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T263" t="inlineStr">
@@ -27982,7 +28052,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C264" s="19" t="inlineStr">
         <is>
           <t>C-263</t>
         </is>
@@ -28051,7 +28121,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S264" t="n">
+      <c r="S264" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T264" t="inlineStr">
@@ -28091,7 +28161,7 @@
           <t>Tabel 14</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C265" s="19" t="inlineStr">
         <is>
           <t>C-264</t>
         </is>
@@ -28150,7 +28220,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S265" t="n">
+      <c r="S265" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T265" t="inlineStr">
@@ -28195,7 +28265,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C266" s="19" t="inlineStr">
         <is>
           <t>C-265</t>
         </is>
@@ -28264,7 +28334,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S266" t="n">
+      <c r="S266" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T266" t="inlineStr">
@@ -28304,7 +28374,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C267" s="19" t="inlineStr">
         <is>
           <t>C-266</t>
         </is>
@@ -28373,7 +28443,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S267" t="n">
+      <c r="S267" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T267" t="inlineStr">
@@ -28413,7 +28483,7 @@
           <t>Tabel 17</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C268" s="19" t="inlineStr">
         <is>
           <t>C-267</t>
         </is>
@@ -28472,7 +28542,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S268" t="n">
+      <c r="S268" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T268" t="inlineStr">
@@ -28517,7 +28587,7 @@
           <t>Tabel 17</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C269" s="19" t="inlineStr">
         <is>
           <t>C-268</t>
         </is>
@@ -28581,7 +28651,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S269" t="n">
+      <c r="S269" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T269" t="inlineStr">
@@ -28626,7 +28696,7 @@
           <t>Figuur 16</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C270" s="19" t="inlineStr">
         <is>
           <t>C-269</t>
         </is>
@@ -28690,7 +28760,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S270" t="n">
+      <c r="S270" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T270" t="inlineStr">
@@ -28735,7 +28805,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C271" s="19" t="inlineStr">
         <is>
           <t>C-270</t>
         </is>
@@ -28804,7 +28874,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S271" t="n">
+      <c r="S271" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T271" t="inlineStr">
@@ -28849,7 +28919,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C272" s="19" t="inlineStr">
         <is>
           <t>C-271</t>
         </is>
@@ -28918,7 +28988,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S272" t="n">
+      <c r="S272" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T272" t="inlineStr">
@@ -28963,7 +29033,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="19" t="inlineStr">
         <is>
           <t>C-272</t>
         </is>
@@ -29032,7 +29102,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S273" t="n">
+      <c r="S273" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T273" t="inlineStr">
@@ -29077,7 +29147,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C274" s="19" t="inlineStr">
         <is>
           <t>C-273</t>
         </is>
@@ -29141,7 +29211,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S274" t="n">
+      <c r="S274" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T274" t="inlineStr">
@@ -29181,7 +29251,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C275" s="19" t="inlineStr">
         <is>
           <t>C-274</t>
         </is>
@@ -29250,7 +29320,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S275" t="n">
+      <c r="S275" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T275" t="inlineStr">
@@ -29290,7 +29360,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C276" s="19" t="inlineStr">
         <is>
           <t>C-275</t>
         </is>
@@ -29359,7 +29429,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S276" t="n">
+      <c r="S276" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T276" t="inlineStr">
@@ -29399,7 +29469,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C277" s="19" t="inlineStr">
         <is>
           <t>C-276</t>
         </is>
@@ -29463,7 +29533,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S277" t="n">
+      <c r="S277" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T277" t="inlineStr">
@@ -29503,7 +29573,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C278" s="19" t="inlineStr">
         <is>
           <t>C-277</t>
         </is>
@@ -29567,7 +29637,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S278" t="n">
+      <c r="S278" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T278" t="inlineStr">
@@ -29593,6 +29663,11 @@
       <c r="X278" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z278" s="20" t="inlineStr">
+        <is>
+          <t>counts 100.000 stuks huiden as if they were tonnes.</t>
         </is>
       </c>
     </row>
@@ -29607,7 +29682,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C279" s="19" t="inlineStr">
         <is>
           <t>C-278</t>
         </is>
@@ -29676,7 +29751,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S279" t="n">
+      <c r="S279" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T279" t="inlineStr">
@@ -29716,7 +29791,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C280" s="19" t="inlineStr">
         <is>
           <t>C-279</t>
         </is>
@@ -29775,7 +29850,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S280" t="n">
+      <c r="S280" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T280" t="inlineStr">
@@ -29815,7 +29890,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C281" s="19" t="inlineStr">
         <is>
           <t>C-280</t>
         </is>
@@ -29874,7 +29949,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S281" t="n">
+      <c r="S281" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T281" t="inlineStr">
@@ -29914,7 +29989,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C282" s="19" t="inlineStr">
         <is>
           <t>C-281</t>
         </is>
@@ -29978,7 +30053,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S282" t="n">
+      <c r="S282" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T282" t="inlineStr">
@@ -30018,14 +30093,14 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C283" s="19" t="inlineStr">
         <is>
           <t>C-282</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van zuivelproducten, productie nevenstromen en productieresiduen</t>
+          <t>AGGREGAAT - Vervaardiging van zuivelproducten, productie nevenstromen en productieresiduen (cijferbasis 2018, door de bron overgenomen)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -30082,7 +30157,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S283" t="n">
+      <c r="S283" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T283" t="inlineStr">
@@ -30122,7 +30197,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C284" s="19" t="inlineStr">
         <is>
           <t>C-283</t>
         </is>
@@ -30181,7 +30256,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S284" t="n">
+      <c r="S284" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T284" t="inlineStr">
@@ -30221,7 +30296,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C285" s="19" t="inlineStr">
         <is>
           <t>C-284</t>
         </is>
@@ -30280,7 +30355,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S285" t="n">
+      <c r="S285" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T285" t="inlineStr">
@@ -30320,7 +30395,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="19" t="inlineStr">
         <is>
           <t>C-285</t>
         </is>
@@ -30379,7 +30454,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S286" t="n">
+      <c r="S286" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T286" t="inlineStr">
@@ -30419,7 +30494,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="C287" s="19" t="inlineStr">
         <is>
           <t>C-286</t>
         </is>
@@ -30478,7 +30553,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S287" t="n">
+      <c r="S287" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T287" t="inlineStr">
@@ -30518,7 +30593,7 @@
           <t>Tabel 26</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C288" s="19" t="inlineStr">
         <is>
           <t>C-287</t>
         </is>
@@ -30577,7 +30652,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S288" t="n">
+      <c r="S288" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T288" t="inlineStr">
@@ -30617,7 +30692,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C289" s="19" t="inlineStr">
         <is>
           <t>C-288</t>
         </is>
@@ -30686,7 +30761,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S289" t="n">
+      <c r="S289" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T289" t="inlineStr">
@@ -30726,7 +30801,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C290" s="19" t="inlineStr">
         <is>
           <t>C-289</t>
         </is>
@@ -30795,7 +30870,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S290" t="n">
+      <c r="S290" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T290" t="inlineStr">
@@ -30835,7 +30910,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
+      <c r="C291" s="19" t="inlineStr">
         <is>
           <t>C-290</t>
         </is>
@@ -30904,7 +30979,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S291" t="n">
+      <c r="S291" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T291" t="inlineStr">
@@ -30944,7 +31019,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C292" s="19" t="inlineStr">
         <is>
           <t>C-291</t>
         </is>
@@ -31013,7 +31088,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S292" t="n">
+      <c r="S292" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T292" t="inlineStr">
@@ -31053,7 +31128,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
+      <c r="C293" s="19" t="inlineStr">
         <is>
           <t>C-292</t>
         </is>
@@ -31122,7 +31197,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S293" t="n">
+      <c r="S293" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T293" t="inlineStr">
@@ -31162,7 +31237,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
+      <c r="C294" s="19" t="inlineStr">
         <is>
           <t>C-293</t>
         </is>
@@ -31231,7 +31306,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S294" t="n">
+      <c r="S294" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T294" t="inlineStr">
@@ -31271,7 +31346,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
+      <c r="C295" s="19" t="inlineStr">
         <is>
           <t>C-294</t>
         </is>
@@ -31340,7 +31415,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S295" t="n">
+      <c r="S295" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T295" t="inlineStr">
@@ -31380,7 +31455,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C296" s="19" t="inlineStr">
         <is>
           <t>C-295</t>
         </is>
@@ -31444,22 +31519,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S296" t="n">
+      <c r="S296" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.11; bron: eetbaar slachtafval wordt in de voedselnijverheid verder verwerkt</t>
+          <t>nevenstroom NACE 10.11; bron: eetbaar slachtafval wordt in de voedselnijverheid verder verwerkt; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W296" t="inlineStr">
@@ -31472,8 +31547,13 @@
           <t>read in PDF</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>eetbaar</t>
+        </is>
+      </c>
     </row>
-    <row r="297">
+    <row r="297" ht="14" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
           <t>81</t>
@@ -31484,7 +31564,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C297" s="19" t="inlineStr">
         <is>
           <t>C-296</t>
         </is>
@@ -31548,22 +31628,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S297" t="n">
+      <c r="S297" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.11</t>
+          <t>nevenstroom NACE 10.11; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
@@ -31588,7 +31668,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C298" s="19" t="inlineStr">
         <is>
           <t>C-297</t>
         </is>
@@ -31652,7 +31732,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S298" t="n">
+      <c r="S298" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T298" t="inlineStr">
@@ -31692,7 +31772,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C299" s="19" t="inlineStr">
         <is>
           <t>C-298</t>
         </is>
@@ -31756,22 +31836,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S299" t="n">
+      <c r="S299" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>nevenstroom</t>
         </is>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>nevenstroom/productieresidu NACE 10.11</t>
+          <t>nevenstroom/productieresidu NACE 10.11; de productnaam van de bron noemt de stroom expliciet niet-eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet.</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
@@ -31796,7 +31876,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C300" s="19" t="inlineStr">
         <is>
           <t>C-299</t>
         </is>
@@ -31826,13 +31906,8 @@
           <t>Gevogelte</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>slachtafval (eetbaar)</t>
-        </is>
-      </c>
       <c r="J300" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -31870,22 +31945,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S300" t="n">
+      <c r="S300" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.12</t>
+          <t>nevenstroom NACE 10.12; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V300" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W300" t="inlineStr">
@@ -31896,6 +31971,11 @@
       <c r="X300" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>eetbaar</t>
         </is>
       </c>
     </row>
@@ -31910,7 +31990,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C301" s="19" t="inlineStr">
         <is>
           <t>C-300</t>
         </is>
@@ -31979,7 +32059,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S301" t="n">
+      <c r="S301" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T301" t="inlineStr">
@@ -32019,7 +32099,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C302" s="19" t="inlineStr">
         <is>
           <t>C-301</t>
         </is>
@@ -32088,7 +32168,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S302" t="n">
+      <c r="S302" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T302" t="inlineStr">
@@ -32128,7 +32208,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C303" s="19" t="inlineStr">
         <is>
           <t>C-302</t>
         </is>
@@ -32192,7 +32272,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S303" t="n">
+      <c r="S303" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T303" t="inlineStr">
@@ -32232,7 +32312,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C304" s="19" t="inlineStr">
         <is>
           <t>C-303</t>
         </is>
@@ -32296,7 +32376,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S304" t="n">
+      <c r="S304" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T304" t="inlineStr">
@@ -32336,7 +32416,7 @@
           <t>Tabel 28</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="C305" s="19" t="inlineStr">
         <is>
           <t>C-304</t>
         </is>
@@ -32400,7 +32480,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S305" t="n">
+      <c r="S305" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T305" t="inlineStr">
@@ -32440,7 +32520,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
+      <c r="C306" s="19" t="inlineStr">
         <is>
           <t>C-305</t>
         </is>
@@ -32509,7 +32589,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S306" t="n">
+      <c r="S306" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T306" t="inlineStr">
@@ -32554,7 +32634,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C307" s="19" t="inlineStr">
         <is>
           <t>C-306</t>
         </is>
@@ -32623,7 +32703,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S307" t="n">
+      <c r="S307" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T307" t="inlineStr">
@@ -32668,7 +32748,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
+      <c r="C308" s="19" t="inlineStr">
         <is>
           <t>C-307</t>
         </is>
@@ -32737,7 +32817,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S308" t="n">
+      <c r="S308" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T308" t="inlineStr">
@@ -32782,7 +32862,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C309" s="19" t="inlineStr">
         <is>
           <t>C-308</t>
         </is>
@@ -32846,22 +32926,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S309" t="n">
+      <c r="S309" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>eigen som van de bron; 'samen 217.672 ton'; komt overeen met Prodcom 101120 + 101240 + 101139 + 101313 = 217.671</t>
+          <t>eigen som van de bron; 'samen 217.672 ton'; komt overeen met Prodcom 101120 + 101240 + 101139 + 101313 = 217.671; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
@@ -32891,7 +32971,7 @@
           <t>Tabel 29</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C310" s="19" t="inlineStr">
         <is>
           <t>C-309</t>
         </is>
@@ -32955,7 +33035,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S310" t="n">
+      <c r="S310" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T310" t="inlineStr">
@@ -33000,7 +33080,7 @@
           <t>Tabel 29</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
+      <c r="C311" s="19" t="inlineStr">
         <is>
           <t>C-310</t>
         </is>
@@ -33064,7 +33144,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S311" t="n">
+      <c r="S311" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T311" t="inlineStr">
@@ -33109,7 +33189,7 @@
           <t>Tabel 29</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
+      <c r="C312" s="19" t="inlineStr">
         <is>
           <t>C-311</t>
         </is>
@@ -33178,7 +33258,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S312" t="n">
+      <c r="S312" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T312" t="inlineStr">
@@ -33218,7 +33298,7 @@
           <t>Tabel 30</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C313" s="19" t="inlineStr">
         <is>
           <t>C-312</t>
         </is>
@@ -33287,7 +33367,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S313" t="n">
+      <c r="S313" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T313" t="inlineStr">
@@ -33332,7 +33412,7 @@
           <t>Tabel 30</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C314" s="19" t="inlineStr">
         <is>
           <t>C-313</t>
         </is>
@@ -33401,7 +33481,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S314" t="n">
+      <c r="S314" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T314" t="inlineStr">
@@ -33446,7 +33526,7 @@
           <t>Tabel 30</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C315" s="19" t="inlineStr">
         <is>
           <t>C-314</t>
         </is>
@@ -33515,7 +33595,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S315" t="n">
+      <c r="S315" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T315" t="inlineStr">
@@ -33560,7 +33640,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
+      <c r="C316" s="21" t="inlineStr">
         <is>
           <t>C-315</t>
         </is>
@@ -33629,7 +33709,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S316" t="n">
+      <c r="S316" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T316" t="inlineStr">
@@ -33639,7 +33719,7 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74)</t>
+          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
@@ -33674,7 +33754,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
+      <c r="C317" s="21" t="inlineStr">
         <is>
           <t>C-316</t>
         </is>
@@ -33733,7 +33813,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S317" t="n">
+      <c r="S317" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T317" t="inlineStr">
@@ -33743,7 +33823,7 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74)</t>
+          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
@@ -33778,7 +33858,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C318" s="21" t="inlineStr">
         <is>
           <t>C-317</t>
         </is>
@@ -33837,7 +33917,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S318" t="n">
+      <c r="S318" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T318" t="inlineStr">
@@ -33847,7 +33927,7 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74)</t>
+          <t>hoofdstroom NACE 10.32; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (p.74) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
@@ -33877,7 +33957,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C319" s="19" t="inlineStr">
         <is>
           <t>C-318</t>
         </is>
@@ -33941,7 +34021,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S319" t="n">
+      <c r="S319" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T319" t="inlineStr">
@@ -33986,14 +34066,14 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
+      <c r="C320" s="19" t="inlineStr">
         <is>
           <t>C-319</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Andere groenten, op andere wijze verduurzaamd dan in azijn (Prodcom 103917)</t>
+          <t>Andere groenten, op andere wijze verduurzaamd dan in azijn of azijnzuur (dus NIET in azijn) (Prodcom 103917)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -34050,7 +34130,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S320" t="n">
+      <c r="S320" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T320" t="inlineStr">
@@ -34076,6 +34156,11 @@
       <c r="X320" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>disjunct van Prodcom 103918 (wel in azijn) - de twee Prodcom-categorieen sluiten elkaar uit en mogen niet als deel/geheel gelezen worden</t>
         </is>
       </c>
     </row>
@@ -34090,14 +34175,14 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C321" s="19" t="inlineStr">
         <is>
           <t>C-320</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Groenten, vruchten en andere eetbare plantendelen, bereid of verduurzaamd in azijn (Prodcom 103918)</t>
+          <t>Groenten, vruchten en andere eetbare plantendelen, bereid of verduurzaamd IN azijn of azijnzuur (Prodcom 103918)</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -34149,7 +34234,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S321" t="n">
+      <c r="S321" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T321" t="inlineStr">
@@ -34175,6 +34260,11 @@
       <c r="X321" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>disjunct van Prodcom 103917 (niet in azijn) - deze rij staat op niveau 2 omdat ze meerdere commoditygroepen omvat, NIET omdat ze een aggregaat van 103917 is</t>
         </is>
       </c>
     </row>
@@ -34189,7 +34279,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
+      <c r="C322" s="19" t="inlineStr">
         <is>
           <t>C-321</t>
         </is>
@@ -34253,7 +34343,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S322" t="n">
+      <c r="S322" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T322" t="inlineStr">
@@ -34293,7 +34383,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
+      <c r="C323" s="19" t="inlineStr">
         <is>
           <t>C-322</t>
         </is>
@@ -34357,7 +34447,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S323" t="n">
+      <c r="S323" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T323" t="inlineStr">
@@ -34397,7 +34487,7 @@
           <t>Tabel 31</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
+      <c r="C324" s="19" t="inlineStr">
         <is>
           <t>C-323</t>
         </is>
@@ -34461,7 +34551,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S324" t="n">
+      <c r="S324" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T324" t="inlineStr">
@@ -34501,7 +34591,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C325" s="19" t="inlineStr">
         <is>
           <t>C-324</t>
         </is>
@@ -34570,7 +34660,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S325" t="n">
+      <c r="S325" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T325" t="inlineStr">
@@ -34610,7 +34700,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C326" s="19" t="inlineStr">
         <is>
           <t>C-325</t>
         </is>
@@ -34679,7 +34769,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S326" t="n">
+      <c r="S326" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T326" t="inlineStr">
@@ -34724,7 +34814,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C327" s="19" t="inlineStr">
         <is>
           <t>C-326</t>
         </is>
@@ -34793,7 +34883,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S327" t="n">
+      <c r="S327" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T327" t="inlineStr">
@@ -34833,7 +34923,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
+      <c r="C328" s="19" t="inlineStr">
         <is>
           <t>C-327</t>
         </is>
@@ -34902,7 +34992,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S328" t="n">
+      <c r="S328" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T328" t="inlineStr">
@@ -34942,7 +35032,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C329" s="19" t="inlineStr">
         <is>
           <t>C-328</t>
         </is>
@@ -35011,7 +35101,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S329" t="n">
+      <c r="S329" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T329" t="inlineStr">
@@ -35051,7 +35141,7 @@
           <t>Tabel 32</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C330" s="19" t="inlineStr">
         <is>
           <t>C-329</t>
         </is>
@@ -35115,7 +35205,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S330" t="n">
+      <c r="S330" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T330" t="inlineStr">
@@ -35160,7 +35250,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C331" s="19" t="inlineStr">
         <is>
           <t>C-330</t>
         </is>
@@ -35229,7 +35319,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S331" t="n">
+      <c r="S331" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T331" t="inlineStr">
@@ -35269,7 +35359,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C332" s="19" t="inlineStr">
         <is>
           <t>C-331</t>
         </is>
@@ -35338,7 +35428,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S332" t="n">
+      <c r="S332" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T332" t="inlineStr">
@@ -35378,7 +35468,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C333" s="19" t="inlineStr">
         <is>
           <t>C-332</t>
         </is>
@@ -35447,7 +35537,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S333" t="n">
+      <c r="S333" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T333" t="inlineStr">
@@ -35487,7 +35577,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C334" s="19" t="inlineStr">
         <is>
           <t>C-333</t>
         </is>
@@ -35556,7 +35646,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S334" t="n">
+      <c r="S334" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T334" t="inlineStr">
@@ -35596,7 +35686,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C335" s="19" t="inlineStr">
         <is>
           <t>C-334</t>
         </is>
@@ -35660,7 +35750,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S335" t="n">
+      <c r="S335" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T335" t="inlineStr">
@@ -35700,7 +35790,7 @@
           <t>Tabel 33</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C336" s="19" t="inlineStr">
         <is>
           <t>C-335</t>
         </is>
@@ -35764,7 +35854,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S336" t="n">
+      <c r="S336" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T336" t="inlineStr">
@@ -35809,7 +35899,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C337" s="19" t="inlineStr">
         <is>
           <t>C-336</t>
         </is>
@@ -35873,7 +35963,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S337" t="n">
+      <c r="S337" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T337" t="inlineStr">
@@ -35913,7 +36003,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
+      <c r="C338" s="19" t="inlineStr">
         <is>
           <t>C-337</t>
         </is>
@@ -35982,7 +36072,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S338" t="n">
+      <c r="S338" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T338" t="inlineStr">
@@ -36022,7 +36112,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C339" s="19" t="inlineStr">
         <is>
           <t>C-338</t>
         </is>
@@ -36091,7 +36181,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S339" t="n">
+      <c r="S339" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T339" t="inlineStr">
@@ -36131,7 +36221,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C340" s="19" t="inlineStr">
         <is>
           <t>C-339</t>
         </is>
@@ -36195,7 +36285,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S340" t="n">
+      <c r="S340" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T340" t="inlineStr">
@@ -36240,7 +36330,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C341" s="19" t="inlineStr">
         <is>
           <t>C-340</t>
         </is>
@@ -36299,7 +36389,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S341" t="n">
+      <c r="S341" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T341" t="inlineStr">
@@ -36344,7 +36434,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C342" s="19" t="inlineStr">
         <is>
           <t>C-341</t>
         </is>
@@ -36403,7 +36493,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S342" t="n">
+      <c r="S342" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T342" t="inlineStr">
@@ -36448,7 +36538,7 @@
           <t>Tabel 34</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C343" s="19" t="inlineStr">
         <is>
           <t>C-342</t>
         </is>
@@ -36512,7 +36602,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S343" t="n">
+      <c r="S343" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T343" t="inlineStr">
@@ -36552,7 +36642,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C344" s="19" t="inlineStr">
         <is>
           <t>C-343</t>
         </is>
@@ -36616,7 +36706,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S344" t="n">
+      <c r="S344" s="24" t="n">
         <v>0.00103</v>
       </c>
       <c r="T344" t="inlineStr">
@@ -36626,7 +36716,7 @@
       </c>
       <c r="U344" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (p.74); Vlaams aandeel 83% (exportratio)</t>
+          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (p.74); Vlaams aandeel 83% (exportratio) Omrekening: 1 liter x 1.030 g/l = 0,00103 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V344" t="inlineStr">
@@ -36661,7 +36751,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C345" s="19" t="inlineStr">
         <is>
           <t>C-344</t>
         </is>
@@ -36725,7 +36815,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S345" t="n">
+      <c r="S345" s="24" t="n">
         <v>0.00103</v>
       </c>
       <c r="T345" t="inlineStr">
@@ -36735,7 +36825,7 @@
       </c>
       <c r="U345" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (p.74)</t>
+          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (p.74) Omrekening: 1 liter x 1.030 g/l = 0,00103 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V345" t="inlineStr">
@@ -36765,7 +36855,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C346" s="19" t="inlineStr">
         <is>
           <t>C-345</t>
         </is>
@@ -36829,7 +36919,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S346" t="n">
+      <c r="S346" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T346" t="inlineStr">
@@ -36869,7 +36959,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C347" s="19" t="inlineStr">
         <is>
           <t>C-346</t>
         </is>
@@ -36933,7 +37023,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S347" t="n">
+      <c r="S347" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T347" t="inlineStr">
@@ -36973,7 +37063,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C348" s="19" t="inlineStr">
         <is>
           <t>C-347</t>
         </is>
@@ -37037,7 +37127,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S348" t="n">
+      <c r="S348" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T348" t="inlineStr">
@@ -37077,7 +37167,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="19" t="inlineStr">
         <is>
           <t>C-348</t>
         </is>
@@ -37141,7 +37231,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S349" t="n">
+      <c r="S349" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T349" t="inlineStr">
@@ -37181,7 +37271,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="19" t="inlineStr">
         <is>
           <t>C-349</t>
         </is>
@@ -37245,7 +37335,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S350" t="n">
+      <c r="S350" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T350" t="inlineStr">
@@ -37285,7 +37375,7 @@
           <t>Tabel 35</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="19" t="inlineStr">
         <is>
           <t>C-350</t>
         </is>
@@ -37349,7 +37439,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S351" t="n">
+      <c r="S351" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T351" t="inlineStr">
@@ -37389,7 +37479,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="19" t="inlineStr">
         <is>
           <t>C-351</t>
         </is>
@@ -37458,7 +37548,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S352" t="n">
+      <c r="S352" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T352" t="inlineStr">
@@ -37503,7 +37593,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="19" t="inlineStr">
         <is>
           <t>C-352</t>
         </is>
@@ -37567,7 +37657,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S353" t="n">
+      <c r="S353" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T353" t="inlineStr">
@@ -37607,7 +37697,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="19" t="inlineStr">
         <is>
           <t>C-353</t>
         </is>
@@ -37671,7 +37761,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S354" t="n">
+      <c r="S354" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T354" t="inlineStr">
@@ -37711,7 +37801,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="19" t="inlineStr">
         <is>
           <t>C-354</t>
         </is>
@@ -37775,7 +37865,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S355" t="n">
+      <c r="S355" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T355" t="inlineStr">
@@ -37815,7 +37905,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="19" t="inlineStr">
         <is>
           <t>C-355</t>
         </is>
@@ -37874,7 +37964,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S356" t="n">
+      <c r="S356" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T356" t="inlineStr">
@@ -37914,7 +38004,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="19" t="inlineStr">
         <is>
           <t>C-356</t>
         </is>
@@ -37973,7 +38063,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S357" t="n">
+      <c r="S357" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T357" t="inlineStr">
@@ -38013,7 +38103,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="19" t="inlineStr">
         <is>
           <t>C-357</t>
         </is>
@@ -38077,7 +38167,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S358" t="n">
+      <c r="S358" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T358" t="inlineStr">
@@ -38122,7 +38212,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="19" t="inlineStr">
         <is>
           <t>C-358</t>
         </is>
@@ -38186,7 +38276,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S359" t="n">
+      <c r="S359" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T359" t="inlineStr">
@@ -38231,7 +38321,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="19" t="inlineStr">
         <is>
           <t>C-359</t>
         </is>
@@ -38295,7 +38385,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S360" t="n">
+      <c r="S360" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T360" t="inlineStr">
@@ -38335,7 +38425,7 @@
           <t>Tabel 36</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="19" t="inlineStr">
         <is>
           <t>C-360</t>
         </is>
@@ -38394,7 +38484,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S361" t="n">
+      <c r="S361" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T361" t="inlineStr">
@@ -38434,14 +38524,14 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="19" t="inlineStr">
         <is>
           <t>C-361</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Riet- en beetwortelsuiker, geraffineerd (Prodcom 108112)</t>
+          <t>Riet- en beetwortelsuiker, geraffineerd - productie van het Vlaamse bedrijf (sites in Vlaanderen en Wallonie) (Prodcom 108112)</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -38498,7 +38588,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S362" t="n">
+      <c r="S362" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T362" t="inlineStr">
@@ -38508,7 +38598,7 @@
       </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.81; Vlaams aandeel 67% (exportproxy); mengt riet- en bietsuiker</t>
+          <t>hoofdstroom NACE 10.81; Vlaams aandeel 67% (exportproxy); mengt riet- en bietsuiker; de bron definieert dit op p.99 als 'de productiehoeveelheid van het Vlaamse bedrijf', waarvan de sites over Vlaanderen en Wallonie verspreid liggen; het is dus GEEN Vlaams grondgebiedcijfer, ook al staat het in de kolom 'Productie Vlaanderen'</t>
         </is>
       </c>
       <c r="V362" t="inlineStr">
@@ -38518,7 +38608,7 @@
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X362" t="inlineStr">
@@ -38528,7 +38618,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>ook in tekst p.99; variant: de bron citeert daar ook Food Industry (2020) met 650.000 ton</t>
+          <t>ook in tekst p.99; hiervan is 289.188 t op Vlaams grondgebied geproduceerd - zie C-379, dat het Vlaamse cijfer is; variant: Food Industry (2020) schat dezelfde bedrijfsproductie op 650.000 t - zie C-380</t>
         </is>
       </c>
     </row>
@@ -38543,7 +38633,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="19" t="inlineStr">
         <is>
           <t>C-362</t>
         </is>
@@ -38607,7 +38697,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S363" t="n">
+      <c r="S363" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T363" t="inlineStr">
@@ -38652,7 +38742,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="19" t="inlineStr">
         <is>
           <t>C-363</t>
         </is>
@@ -38721,7 +38811,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S364" t="n">
+      <c r="S364" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T364" t="inlineStr">
@@ -38761,7 +38851,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="19" t="inlineStr">
         <is>
           <t>C-364</t>
         </is>
@@ -38830,7 +38920,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S365" t="n">
+      <c r="S365" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T365" t="inlineStr">
@@ -38870,7 +38960,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="19" t="inlineStr">
         <is>
           <t>C-365</t>
         </is>
@@ -38929,7 +39019,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S366" t="n">
+      <c r="S366" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T366" t="inlineStr">
@@ -38969,7 +39059,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="19" t="inlineStr">
         <is>
           <t>C-366</t>
         </is>
@@ -39028,7 +39118,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S367" t="n">
+      <c r="S367" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T367" t="inlineStr">
@@ -39068,7 +39158,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="19" t="inlineStr">
         <is>
           <t>C-367</t>
         </is>
@@ -39127,7 +39217,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S368" t="n">
+      <c r="S368" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T368" t="inlineStr">
@@ -39167,7 +39257,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="19" t="inlineStr">
         <is>
           <t>C-368</t>
         </is>
@@ -39226,7 +39316,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S369" t="n">
+      <c r="S369" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T369" t="inlineStr">
@@ -39266,7 +39356,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="19" t="inlineStr">
         <is>
           <t>C-369</t>
         </is>
@@ -39325,7 +39415,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S370" t="n">
+      <c r="S370" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T370" t="inlineStr">
@@ -39365,7 +39455,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="19" t="inlineStr">
         <is>
           <t>C-370</t>
         </is>
@@ -39424,7 +39514,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S371" t="n">
+      <c r="S371" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T371" t="inlineStr">
@@ -39464,7 +39554,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C372" s="19" t="inlineStr">
         <is>
           <t>C-371</t>
         </is>
@@ -39523,7 +39613,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S372" t="n">
+      <c r="S372" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T372" t="inlineStr">
@@ -39563,7 +39653,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C373" s="19" t="inlineStr">
         <is>
           <t>C-372</t>
         </is>
@@ -39622,7 +39712,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S373" t="n">
+      <c r="S373" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T373" t="inlineStr">
@@ -39662,7 +39752,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C374" s="19" t="inlineStr">
         <is>
           <t>C-373</t>
         </is>
@@ -39721,7 +39811,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S374" t="n">
+      <c r="S374" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T374" t="inlineStr">
@@ -39761,7 +39851,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
+      <c r="C375" s="19" t="inlineStr">
         <is>
           <t>C-374</t>
         </is>
@@ -39820,7 +39910,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S375" t="n">
+      <c r="S375" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T375" t="inlineStr">
@@ -39860,7 +39950,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C376" s="19" t="inlineStr">
         <is>
           <t>C-375</t>
         </is>
@@ -39924,7 +40014,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S376" t="n">
+      <c r="S376" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T376" t="inlineStr">
@@ -39964,7 +40054,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C377" s="19" t="inlineStr">
         <is>
           <t>C-376</t>
         </is>
@@ -40023,7 +40113,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S377" t="n">
+      <c r="S377" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T377" t="inlineStr">
@@ -40063,7 +40153,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
+      <c r="C378" s="19" t="inlineStr">
         <is>
           <t>C-377</t>
         </is>
@@ -40122,7 +40212,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S378" t="n">
+      <c r="S378" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T378" t="inlineStr">
@@ -40162,7 +40252,7 @@
           <t>Tabel 37</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
+      <c r="C379" s="19" t="inlineStr">
         <is>
           <t>C-378</t>
         </is>
@@ -40221,7 +40311,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S379" t="n">
+      <c r="S379" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T379" t="inlineStr">
@@ -40261,14 +40351,14 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C380" s="19" t="inlineStr">
         <is>
           <t>C-379</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Suikerproductie op Vlaamse productiesites (grondgebiedbasis)</t>
+          <t>Suikerproductie op Vlaams grondgebied (35% van de Belgische productie) - het Vlaamse cijfer</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -40325,7 +40415,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S380" t="n">
+      <c r="S380" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T380" t="inlineStr">
@@ -40355,7 +40445,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>parallelle afbakening naast de 556.283 ton van Tabel 37 (exportproxy 67%) - niet optellen</t>
+          <t>deelverzameling van de 556.283 t bedrijfsproductie in C-361 (Belgie), niet een alternatieve meting daarvan - niet optellen</t>
         </is>
       </c>
     </row>
@@ -40370,14 +40460,14 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C381" s="19" t="inlineStr">
         <is>
           <t>C-380</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Suikerproductie Vlaanderen volgens Food Industry (2020)</t>
+          <t>Suikerproductie van het Vlaamse bedrijf volgens Food Industry (2020) (sites in Vlaanderen en Wallonie)</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -40434,7 +40524,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S381" t="n">
+      <c r="S381" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T381" t="inlineStr">
@@ -40444,7 +40534,7 @@
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>schatting van een derde bron die de bron zelf naast haar eigen 556.283 ton plaatst</t>
+          <t>schatting van een derde bron die de bron zelf naast haar eigen 556.283 ton plaatst; betreft dezelfde bedrijfsafbakening als C-361 en dus geen Vlaams grondgebiedcijfer</t>
         </is>
       </c>
       <c r="V381" t="inlineStr">
@@ -40454,7 +40544,7 @@
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X381" t="inlineStr">
@@ -40464,7 +40554,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>variant van de 556.283 ton uit Tabel 37 (p.100)</t>
+          <t>variant van de 556.283 t in C-361 (zelfde bedrijfsafbakening); het Vlaamse grondgebiedcijfer is C-379</t>
         </is>
       </c>
     </row>
@@ -40479,7 +40569,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C382" s="19" t="inlineStr">
         <is>
           <t>C-381</t>
         </is>
@@ -40543,7 +40633,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S382" t="n">
+      <c r="S382" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T382" t="inlineStr">
@@ -40588,7 +40678,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C383" s="19" t="inlineStr">
         <is>
           <t>C-382</t>
         </is>
@@ -40662,7 +40752,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S383" t="n">
+      <c r="S383" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T383" t="inlineStr">
@@ -40702,7 +40792,7 @@
           <t>tekst</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C384" s="19" t="inlineStr">
         <is>
           <t>C-383</t>
         </is>
@@ -40761,7 +40851,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S384" t="n">
+      <c r="S384" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T384" t="inlineStr">
@@ -40806,7 +40896,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C385" s="19" t="inlineStr">
         <is>
           <t>C-384</t>
         </is>
@@ -40865,7 +40955,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S385" t="n">
+      <c r="S385" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T385" t="inlineStr">
@@ -40891,6 +40981,11 @@
       <c r="X385" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Z385" t="inlineStr">
@@ -40910,7 +41005,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C386" s="19" t="inlineStr">
         <is>
           <t>C-385</t>
         </is>
@@ -40969,7 +41064,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S386" t="n">
+      <c r="S386" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T386" t="inlineStr">
@@ -40995,6 +41090,11 @@
       <c r="X386" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -41009,7 +41109,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
+      <c r="C387" s="19" t="inlineStr">
         <is>
           <t>C-386</t>
         </is>
@@ -41068,7 +41168,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S387" t="n">
+      <c r="S387" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T387" t="inlineStr">
@@ -41094,6 +41194,11 @@
       <c r="X387" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -41108,7 +41213,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C388" s="19" t="inlineStr">
         <is>
           <t>C-387</t>
         </is>
@@ -41167,7 +41272,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S388" t="n">
+      <c r="S388" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T388" t="inlineStr">
@@ -41193,6 +41298,11 @@
       <c r="X388" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -41207,7 +41317,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C389" s="19" t="inlineStr">
         <is>
           <t>C-388</t>
         </is>
@@ -41266,7 +41376,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S389" t="n">
+      <c r="S389" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T389" t="inlineStr">
@@ -41292,6 +41402,11 @@
       <c r="X389" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -41306,7 +41421,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
+      <c r="C390" s="19" t="inlineStr">
         <is>
           <t>C-389</t>
         </is>
@@ -41365,7 +41480,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S390" t="n">
+      <c r="S390" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T390" t="inlineStr">
@@ -41391,6 +41506,11 @@
       <c r="X390" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -41405,7 +41525,7 @@
           <t>Tabel 39</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C391" s="19" t="inlineStr">
         <is>
           <t>C-390</t>
         </is>
@@ -41464,7 +41584,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S391" t="n">
+      <c r="S391" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T391" t="inlineStr">
@@ -41490,6 +41610,11 @@
       <c r="X391" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Z391" t="inlineStr">
@@ -41509,7 +41634,7 @@
           <t>Tabel 40</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C392" s="19" t="inlineStr">
         <is>
           <t>C-391</t>
         </is>
@@ -41568,7 +41693,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S392" t="n">
+      <c r="S392" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T392" t="inlineStr">
@@ -41608,7 +41733,7 @@
           <t>Tabel 40</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C393" s="19" t="inlineStr">
         <is>
           <t>C-392</t>
         </is>
@@ -41667,7 +41792,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S393" t="n">
+      <c r="S393" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T393" t="inlineStr">
@@ -41707,7 +41832,7 @@
           <t>Tabel 41</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C394" s="19" t="inlineStr">
         <is>
           <t>C-393</t>
         </is>
@@ -41771,7 +41896,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S394" t="n">
+      <c r="S394" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T394" t="inlineStr">
@@ -41781,7 +41906,7 @@
       </c>
       <c r="U394" t="inlineStr">
         <is>
-          <t>de federatie vertegenwoordigt 95% van het Belgische productievolume; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75)</t>
+          <t>de federatie vertegenwoordigt 95% van het Belgische productievolume; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V394" t="inlineStr">
@@ -41797,6 +41922,11 @@
       <c r="X394" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Z394" t="inlineStr">
@@ -41816,7 +41946,7 @@
           <t>Tabel 41</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C395" s="19" t="inlineStr">
         <is>
           <t>C-394</t>
         </is>
@@ -41880,7 +42010,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S395" t="n">
+      <c r="S395" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T395" t="inlineStr">
@@ -41890,7 +42020,7 @@
       </c>
       <c r="U395" t="inlineStr">
         <is>
-          <t>Statbel-cijfer; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75)</t>
+          <t>Statbel-cijfer; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V395" t="inlineStr">
@@ -41906,6 +42036,11 @@
       <c r="X395" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Z395" t="inlineStr">
@@ -41925,7 +42060,7 @@
           <t>Tabel 41</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C396" s="19" t="inlineStr">
         <is>
           <t>C-395</t>
         </is>
@@ -41989,7 +42124,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S396" t="n">
+      <c r="S396" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T396" t="inlineStr">
@@ -41999,7 +42134,7 @@
       </c>
       <c r="U396" t="inlineStr">
         <is>
-          <t>Vlaams aandeel 76% (exportratio); omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75)</t>
+          <t>Vlaams aandeel 76% (exportratio); omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (p.75) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V396" t="inlineStr">
@@ -42034,7 +42169,7 @@
           <t>Tabel 42</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C397" s="19" t="inlineStr">
         <is>
           <t>C-396</t>
         </is>
@@ -42098,7 +42233,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S397" t="n">
+      <c r="S397" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T397" t="inlineStr">
@@ -42132,110 +42267,110 @@
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="398" customFormat="1" s="17">
+      <c r="A398" s="17" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B398" s="17" t="inlineStr">
         <is>
           <t>Tabel 42</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C398" s="22" t="inlineStr">
         <is>
           <t>C-397</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
+      <c r="D398" s="17" t="inlineStr">
         <is>
           <t>Bostel (brouwerijafval) en afvallen van branderijen (Prodcom 110520)</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
+      <c r="E398" s="17" t="inlineStr">
         <is>
           <t>Reststroom</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
+      <c r="F398" s="17" t="inlineStr">
         <is>
           <t>Plantaardig - akkerbouw</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
+      <c r="G398" s="17" t="inlineStr">
         <is>
           <t>Granen</t>
         </is>
       </c>
-      <c r="J398" t="n">
+      <c r="J398" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K398" t="inlineStr">
+      <c r="K398" s="17" t="inlineStr">
         <is>
           <t>Vervaardiging van dranken (NACE 11)</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
+      <c r="L398" s="17" t="inlineStr">
         <is>
           <t>Voedingsindustrie</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr">
+      <c r="M398" s="17" t="inlineStr">
         <is>
           <t>S091</t>
         </is>
       </c>
-      <c r="N398" t="inlineStr">
+      <c r="N398" s="17" t="inlineStr">
         <is>
           <t>MONBIO 4.0</t>
         </is>
       </c>
-      <c r="O398" t="inlineStr">
+      <c r="O398" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="P398" t="n">
+      <c r="P398" s="17" t="n">
         <v>134653</v>
       </c>
-      <c r="Q398" t="n">
+      <c r="Q398" s="17" t="n">
         <v>134653</v>
       </c>
-      <c r="R398" t="inlineStr">
+      <c r="R398" s="17" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="S398" t="n">
+      <c r="S398" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="T398" t="inlineStr">
+      <c r="T398" s="17" t="inlineStr">
         <is>
           <t>agri-food waste</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="U398" s="17" t="inlineStr">
         <is>
           <t>belangrijkste nevenstroom van het brouwproces; bron noemt het cijfer 'hoogstwaarschijnlijk een onderschatting of onderrapportering'</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
+      <c r="V398" s="17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="W398" t="inlineStr">
+      <c r="W398" s="17" t="inlineStr">
         <is>
           <t>Vlaanderen</t>
         </is>
       </c>
-      <c r="X398" t="inlineStr">
+      <c r="X398" s="17" t="inlineStr">
         <is>
           <t>read in PDF</t>
         </is>
       </c>
-      <c r="Z398" t="inlineStr">
+      <c r="Z398" s="17" t="inlineStr">
         <is>
           <t>afgerond 135 kton in Tabel 26 (p.76); de Belgische Prodcom-waarde is 176.989 ton (tekst p.106)</t>
         </is>
@@ -42311,7 +42446,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S399" t="n">
+      <c r="S399" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T399" t="inlineStr">
@@ -42415,7 +42550,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S400" t="n">
+      <c r="S400" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T400" t="inlineStr">
@@ -42425,7 +42560,7 @@
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>hoofdstromen uit de landbouwteelten</t>
+          <t>hoofdstromen uit de landbouwteelten; LET OP: dit totaal OMVAT de sierteelt, die als niet-agrovoeding niet apart gecapteerd is, zodat de gecapteerde gewasgroeprijen niet tot dit totaal sommeren</t>
         </is>
       </c>
       <c r="V400" t="inlineStr">
@@ -42524,7 +42659,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S401" t="n">
+      <c r="S401" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T401" t="inlineStr">
@@ -42628,7 +42763,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S402" t="n">
+      <c r="S402" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T402" t="inlineStr">
@@ -42732,7 +42867,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S403" t="n">
+      <c r="S403" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T403" t="inlineStr">
@@ -42836,7 +42971,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S404" t="n">
+      <c r="S404" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T404" t="inlineStr">
@@ -42940,7 +43075,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S405" t="n">
+      <c r="S405" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T405" t="inlineStr">
@@ -43044,7 +43179,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S406" t="n">
+      <c r="S406" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T406" t="inlineStr">
@@ -43148,7 +43283,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S407" t="n">
+      <c r="S407" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T407" t="inlineStr">
@@ -43252,7 +43387,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S408" t="n">
+      <c r="S408" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T408" t="inlineStr">
@@ -43361,7 +43496,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S409" t="n">
+      <c r="S409" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T409" t="inlineStr">
@@ -43470,7 +43605,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S410" t="n">
+      <c r="S410" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T410" t="inlineStr">
@@ -43579,7 +43714,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S411" t="n">
+      <c r="S411" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T411" t="inlineStr">
@@ -43688,7 +43823,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S412" t="n">
+      <c r="S412" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T412" t="inlineStr">
@@ -43797,7 +43932,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S413" t="n">
+      <c r="S413" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T413" t="inlineStr">
@@ -43906,7 +44041,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S414" t="n">
+      <c r="S414" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T414" t="inlineStr">
@@ -44015,7 +44150,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S415" t="n">
+      <c r="S415" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T415" t="inlineStr">
@@ -44124,7 +44259,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S416" t="n">
+      <c r="S416" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T416" t="inlineStr">
@@ -44233,7 +44368,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S417" t="n">
+      <c r="S417" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T417" t="inlineStr">
@@ -44342,7 +44477,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S418" t="n">
+      <c r="S418" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T418" t="inlineStr">
@@ -44451,7 +44586,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S419" t="n">
+      <c r="S419" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T419" t="inlineStr">
@@ -44550,7 +44685,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S420" t="n">
+      <c r="S420" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T420" t="inlineStr">
@@ -44659,7 +44794,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S421" t="n">
+      <c r="S421" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T421" t="inlineStr">
@@ -44763,7 +44898,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S422" t="n">
+      <c r="S422" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T422" t="inlineStr">
@@ -44867,7 +45002,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S423" t="n">
+      <c r="S423" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T423" t="inlineStr">
@@ -44971,7 +45106,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S424" t="n">
+      <c r="S424" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T424" t="inlineStr">
@@ -45075,7 +45210,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S425" t="n">
+      <c r="S425" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T425" t="inlineStr">
@@ -45179,7 +45314,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S426" t="n">
+      <c r="S426" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T426" t="inlineStr">
@@ -45283,7 +45418,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S427" t="n">
+      <c r="S427" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T427" t="inlineStr">
@@ -45402,7 +45537,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S428" t="n">
+      <c r="S428" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T428" t="inlineStr">
@@ -45516,7 +45651,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S429" t="n">
+      <c r="S429" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T429" t="inlineStr">
@@ -45630,7 +45765,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S430" t="n">
+      <c r="S430" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T430" t="inlineStr">
@@ -45744,7 +45879,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S431" t="n">
+      <c r="S431" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T431" t="inlineStr">
@@ -45858,7 +45993,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S432" t="n">
+      <c r="S432" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T432" t="inlineStr">
@@ -45977,7 +46112,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S433" t="n">
+      <c r="S433" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T433" t="inlineStr">
@@ -46091,7 +46226,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S434" t="n">
+      <c r="S434" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T434" t="inlineStr">
@@ -46205,7 +46340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S435" t="n">
+      <c r="S435" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T435" t="inlineStr">
@@ -46319,7 +46454,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S436" t="n">
+      <c r="S436" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T436" t="inlineStr">
@@ -46433,7 +46568,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S437" t="n">
+      <c r="S437" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T437" t="inlineStr">
@@ -46547,7 +46682,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S438" t="n">
+      <c r="S438" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T438" t="inlineStr">
@@ -46656,7 +46791,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S439" t="n">
+      <c r="S439" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T439" t="inlineStr">
@@ -46765,7 +46900,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S440" t="n">
+      <c r="S440" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T440" t="inlineStr">
@@ -46874,7 +47009,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S441" t="n">
+      <c r="S441" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T441" t="inlineStr">
@@ -46983,7 +47118,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S442" t="n">
+      <c r="S442" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T442" t="inlineStr">
@@ -47092,7 +47227,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S443" t="n">
+      <c r="S443" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T443" t="inlineStr">
@@ -47196,7 +47331,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S444" t="n">
+      <c r="S444" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T444" t="inlineStr">
@@ -47305,7 +47440,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S445" t="n">
+      <c r="S445" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T445" t="inlineStr">
@@ -47404,7 +47539,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S446" t="n">
+      <c r="S446" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T446" t="inlineStr">
@@ -47518,7 +47653,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S447" t="n">
+      <c r="S447" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T447" t="inlineStr">
@@ -47627,7 +47762,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S448" t="n">
+      <c r="S448" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T448" t="inlineStr">
@@ -47726,7 +47861,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S449" t="n">
+      <c r="S449" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T449" t="inlineStr">
@@ -47835,7 +47970,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S450" t="n">
+      <c r="S450" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T450" t="inlineStr">
@@ -47949,7 +48084,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S451" t="n">
+      <c r="S451" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T451" t="inlineStr">
@@ -48063,7 +48198,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S452" t="n">
+      <c r="S452" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T452" t="inlineStr">
@@ -48177,7 +48312,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S453" t="n">
+      <c r="S453" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T453" t="inlineStr">
@@ -48286,7 +48421,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S454" t="n">
+      <c r="S454" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T454" t="inlineStr">
@@ -48400,7 +48535,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S455" t="n">
+      <c r="S455" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T455" t="inlineStr">
@@ -48514,7 +48649,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S456" t="n">
+      <c r="S456" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T456" t="inlineStr">
@@ -48628,7 +48763,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S457" t="n">
+      <c r="S457" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T457" t="inlineStr">
@@ -48737,7 +48872,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S458" t="n">
+      <c r="S458" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T458" t="inlineStr">
@@ -48846,7 +48981,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S459" t="n">
+      <c r="S459" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T459" t="inlineStr">
@@ -48955,7 +49090,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S460" t="n">
+      <c r="S460" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T460" t="inlineStr">
@@ -49064,7 +49199,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S461" t="n">
+      <c r="S461" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T461" t="inlineStr">
@@ -49168,7 +49303,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S462" t="n">
+      <c r="S462" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T462" t="inlineStr">
@@ -49272,7 +49407,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S463" t="n">
+      <c r="S463" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T463" t="inlineStr">
@@ -49381,7 +49516,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S464" t="n">
+      <c r="S464" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T464" t="inlineStr">
@@ -49480,7 +49615,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S465" t="n">
+      <c r="S465" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T465" t="inlineStr">
@@ -49579,7 +49714,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S466" t="n">
+      <c r="S466" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T466" t="inlineStr">
@@ -49683,7 +49818,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S467" t="n">
+      <c r="S467" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T467" t="inlineStr">
@@ -49730,7 +49865,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van zuivelproducten, productie nevenstromen en productieresiduen</t>
+          <t>AGGREGAAT - Vervaardiging van zuivelproducten, productie nevenstromen en productieresiduen (cijferbasis 2018, door de bron overgenomen)</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -49787,7 +49922,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S468" t="n">
+      <c r="S468" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T468" t="inlineStr">
@@ -49886,7 +50021,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S469" t="n">
+      <c r="S469" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T469" t="inlineStr">
@@ -49985,7 +50120,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S470" t="n">
+      <c r="S470" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T470" t="inlineStr">
@@ -50084,7 +50219,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S471" t="n">
+      <c r="S471" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T471" t="inlineStr">
@@ -50183,7 +50318,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S472" t="n">
+      <c r="S472" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T472" t="inlineStr">
@@ -50282,7 +50417,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S473" t="n">
+      <c r="S473" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T473" t="inlineStr">
@@ -50391,7 +50526,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S474" t="n">
+      <c r="S474" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T474" t="inlineStr">
@@ -50500,7 +50635,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S475" t="n">
+      <c r="S475" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T475" t="inlineStr">
@@ -50609,7 +50744,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S476" t="n">
+      <c r="S476" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T476" t="inlineStr">
@@ -50718,7 +50853,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S477" t="n">
+      <c r="S477" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T477" t="inlineStr">
@@ -50827,7 +50962,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S478" t="n">
+      <c r="S478" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T478" t="inlineStr">
@@ -50936,7 +51071,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S479" t="n">
+      <c r="S479" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T479" t="inlineStr">
@@ -51045,7 +51180,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S480" t="n">
+      <c r="S480" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T480" t="inlineStr">
@@ -51149,22 +51284,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S481" t="n">
+      <c r="S481" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U481" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.11</t>
+          <t>nevenstroom NACE 10.11; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V481" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W481" t="inlineStr">
@@ -51253,22 +51388,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S482" t="n">
+      <c r="S482" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U482" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.11</t>
+          <t>nevenstroom NACE 10.11; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V482" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W482" t="inlineStr">
@@ -51357,7 +51492,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S483" t="n">
+      <c r="S483" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T483" t="inlineStr">
@@ -51461,22 +51596,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S484" t="n">
+      <c r="S484" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T484" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>nevenstroom</t>
         </is>
       </c>
       <c r="U484" t="inlineStr">
         <is>
-          <t>nevenstroom/productieresidu NACE 10.11</t>
+          <t>nevenstroom/productieresidu NACE 10.11; de productnaam van de bron noemt de stroom expliciet niet-eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet.</t>
         </is>
       </c>
       <c r="V484" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W484" t="inlineStr">
@@ -51531,13 +51666,8 @@
           <t>Gevogelte</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>slachtafval (eetbaar)</t>
-        </is>
-      </c>
       <c r="J485" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
@@ -51575,22 +51705,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S485" t="n">
+      <c r="S485" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T485" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U485" t="inlineStr">
         <is>
-          <t>nevenstroom NACE 10.12</t>
+          <t>nevenstroom NACE 10.12; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V485" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W485" t="inlineStr">
@@ -51684,7 +51814,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S486" t="n">
+      <c r="S486" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T486" t="inlineStr">
@@ -51793,7 +51923,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S487" t="n">
+      <c r="S487" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T487" t="inlineStr">
@@ -51897,7 +52027,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S488" t="n">
+      <c r="S488" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T488" t="inlineStr">
@@ -52001,7 +52131,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S489" t="n">
+      <c r="S489" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T489" t="inlineStr">
@@ -52105,7 +52235,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S490" t="n">
+      <c r="S490" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T490" t="inlineStr">
@@ -52214,7 +52344,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S491" t="n">
+      <c r="S491" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T491" t="inlineStr">
@@ -52328,7 +52458,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S492" t="n">
+      <c r="S492" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T492" t="inlineStr">
@@ -52442,7 +52572,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S493" t="n">
+      <c r="S493" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T493" t="inlineStr">
@@ -52551,22 +52681,22 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S494" t="n">
+      <c r="S494" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T494" t="inlineStr">
         <is>
-          <t>agri-food waste</t>
+          <t>voedselverlies</t>
         </is>
       </c>
       <c r="U494" t="inlineStr">
         <is>
-          <t>eigen som van de bron; 'samen 215.958 ton'; Prodcom 101120 + 101139 + 101240 geven 215.957</t>
+          <t>eigen som van de bron; 'samen 215.958 ton'; Prodcom 101120 + 101139 + 101240 geven 215.957; de productnaam van de bron noemt de stroom expliciet eetbaar, dus de eetbaar/oneetbaar-opsplitsing is hier wel gespecificeerd en de sessiestandaard 'agri-food waste' geldt niet. LET OP: de bron benadrukt dat deze eetbare slachtafvallen verder verwerkt worden in de voedselnijverheid; het gaat dus om een gevaloriseerde nevenstroom, niet om verlies - 'voedselverlies' is hier de eetbare-fractie-categorie van het register, geen uitspraak over verspilling</t>
         </is>
       </c>
       <c r="V494" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="W494" t="inlineStr">
@@ -52660,7 +52790,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S495" t="n">
+      <c r="S495" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T495" t="inlineStr">
@@ -52769,7 +52899,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S496" t="n">
+      <c r="S496" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T496" t="inlineStr">
@@ -52878,7 +53008,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S497" t="n">
+      <c r="S497" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T497" t="inlineStr">
@@ -52992,7 +53122,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S498" t="n">
+      <c r="S498" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T498" t="inlineStr">
@@ -53101,7 +53231,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S499" t="n">
+      <c r="S499" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T499" t="inlineStr">
@@ -53210,7 +53340,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S500" t="n">
+      <c r="S500" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T500" t="inlineStr">
@@ -53324,7 +53454,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S501" t="n">
+      <c r="S501" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T501" t="inlineStr">
@@ -53438,7 +53568,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S502" t="n">
+      <c r="S502" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T502" t="inlineStr">
@@ -53542,7 +53672,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S503" t="n">
+      <c r="S503" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T503" t="inlineStr">
@@ -53552,7 +53682,7 @@
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen)</t>
+          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V503" t="inlineStr">
@@ -53641,7 +53771,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S504" t="n">
+      <c r="S504" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T504" t="inlineStr">
@@ -53651,7 +53781,7 @@
       </c>
       <c r="U504" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen)</t>
+          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V504" t="inlineStr">
@@ -53750,7 +53880,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S505" t="n">
+      <c r="S505" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T505" t="inlineStr">
@@ -53760,7 +53890,7 @@
       </c>
       <c r="U505" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen)</t>
+          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V505" t="inlineStr">
@@ -53854,7 +53984,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S506" t="n">
+      <c r="S506" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T506" t="inlineStr">
@@ -53864,7 +53994,7 @@
       </c>
       <c r="U506" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen)</t>
+          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V506" t="inlineStr">
@@ -53958,7 +54088,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S507" t="n">
+      <c r="S507" s="24" t="n">
         <v>0.00104</v>
       </c>
       <c r="T507" t="inlineStr">
@@ -53968,7 +54098,7 @@
       </c>
       <c r="U507" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen)</t>
+          <t>hoofdstroom NACE 10.32/10.39; omrekening met het door de bron opgegeven soortelijk gewicht van 1.040 g/l (folio 106); Vlaams aandeel 97% (exportratio sappen) Omrekening: 1 liter x 1.040 g/l = 0,00104 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V507" t="inlineStr">
@@ -54062,7 +54192,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S508" t="n">
+      <c r="S508" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T508" t="inlineStr">
@@ -54114,7 +54244,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Andere groenten, op andere wijze verduurzaamd dan in azijn (Prodcom 103917)</t>
+          <t>Andere groenten, op andere wijze verduurzaamd dan in azijn of azijnzuur (dus NIET in azijn) (Prodcom 103917)</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -54171,7 +54301,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S509" t="n">
+      <c r="S509" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T509" t="inlineStr">
@@ -54197,6 +54327,11 @@
       <c r="X509" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
+        <is>
+          <t>disjunct van Prodcom 103918 (wel in azijn) - de twee Prodcom-categorieen sluiten elkaar uit en mogen niet als deel/geheel gelezen worden</t>
         </is>
       </c>
     </row>
@@ -54218,7 +54353,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Groenten, vruchten en andere eetbare plantendelen, bereid of verduurzaamd in azijn (Prodcom 103918)</t>
+          <t>Groenten, vruchten en andere eetbare plantendelen, bereid of verduurzaamd IN azijn of azijnzuur (Prodcom 103918)</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -54270,7 +54405,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S510" t="n">
+      <c r="S510" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T510" t="inlineStr">
@@ -54296,6 +54431,11 @@
       <c r="X510" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
+        <is>
+          <t>disjunct van Prodcom 103917 (niet in azijn) - deze rij staat op niveau 2 omdat ze meerdere commoditygroepen omvat, NIET omdat ze een aggregaat van 103917 is</t>
         </is>
       </c>
     </row>
@@ -54374,7 +54514,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S511" t="n">
+      <c r="S511" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T511" t="inlineStr">
@@ -54478,7 +54618,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S512" t="n">
+      <c r="S512" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T512" t="inlineStr">
@@ -54582,7 +54722,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S513" t="n">
+      <c r="S513" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T513" t="inlineStr">
@@ -54691,7 +54831,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S514" t="n">
+      <c r="S514" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T514" t="inlineStr">
@@ -54800,7 +54940,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S515" t="n">
+      <c r="S515" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T515" t="inlineStr">
@@ -54914,7 +55054,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S516" t="n">
+      <c r="S516" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T516" t="inlineStr">
@@ -55023,7 +55163,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S517" t="n">
+      <c r="S517" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T517" t="inlineStr">
@@ -55132,7 +55272,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S518" t="n">
+      <c r="S518" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T518" t="inlineStr">
@@ -55236,7 +55376,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S519" t="n">
+      <c r="S519" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T519" t="inlineStr">
@@ -55350,7 +55490,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S520" t="n">
+      <c r="S520" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T520" t="inlineStr">
@@ -55459,7 +55599,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S521" t="n">
+      <c r="S521" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T521" t="inlineStr">
@@ -55568,7 +55708,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S522" t="n">
+      <c r="S522" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T522" t="inlineStr">
@@ -55677,7 +55817,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S523" t="n">
+      <c r="S523" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T523" t="inlineStr">
@@ -55781,7 +55921,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S524" t="n">
+      <c r="S524" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T524" t="inlineStr">
@@ -55885,7 +56025,7 @@
           <t>kton</t>
         </is>
       </c>
-      <c r="S525" t="n">
+      <c r="S525" s="24" t="n">
         <v>1000</v>
       </c>
       <c r="T525" t="inlineStr">
@@ -55994,7 +56134,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S526" t="n">
+      <c r="S526" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T526" t="inlineStr">
@@ -56103,7 +56243,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S527" t="n">
+      <c r="S527" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T527" t="inlineStr">
@@ -56212,7 +56352,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S528" t="n">
+      <c r="S528" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T528" t="inlineStr">
@@ -56321,7 +56461,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S529" t="n">
+      <c r="S529" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T529" t="inlineStr">
@@ -56425,7 +56565,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S530" t="n">
+      <c r="S530" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T530" t="inlineStr">
@@ -56529,7 +56669,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S531" t="n">
+      <c r="S531" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T531" t="inlineStr">
@@ -56633,7 +56773,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S532" t="n">
+      <c r="S532" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T532" t="inlineStr">
@@ -56742,7 +56882,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S533" t="n">
+      <c r="S533" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T533" t="inlineStr">
@@ -56846,7 +56986,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S534" t="n">
+      <c r="S534" s="24" t="n">
         <v>0.00103</v>
       </c>
       <c r="T534" t="inlineStr">
@@ -56856,7 +56996,7 @@
       </c>
       <c r="U534" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (folio 106); Vlaams aandeel 81% (exportratio)</t>
+          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (folio 106); Vlaams aandeel 81% (exportratio) Omrekening: 1 liter x 1.030 g/l = 0,00103 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V534" t="inlineStr">
@@ -56955,7 +57095,7 @@
           <t>liter</t>
         </is>
       </c>
-      <c r="S535" t="n">
+      <c r="S535" s="24" t="n">
         <v>0.00103</v>
       </c>
       <c r="T535" t="inlineStr">
@@ -56965,7 +57105,7 @@
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (folio 106)</t>
+          <t>hoofdstroom NACE 10.5; omrekening met het door de bron opgegeven soortelijk gewicht van 1.030 g/l (folio 106) Omrekening: 1 liter x 1.030 g/l = 0,00103 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V535" t="inlineStr">
@@ -57059,7 +57199,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S536" t="n">
+      <c r="S536" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T536" t="inlineStr">
@@ -57163,7 +57303,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S537" t="n">
+      <c r="S537" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T537" t="inlineStr">
@@ -57267,7 +57407,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S538" t="n">
+      <c r="S538" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T538" t="inlineStr">
@@ -57371,7 +57511,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S539" t="n">
+      <c r="S539" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T539" t="inlineStr">
@@ -57475,7 +57615,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S540" t="n">
+      <c r="S540" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T540" t="inlineStr">
@@ -57579,7 +57719,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S541" t="n">
+      <c r="S541" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T541" t="inlineStr">
@@ -57683,7 +57823,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S542" t="n">
+      <c r="S542" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T542" t="inlineStr">
@@ -57792,7 +57932,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S543" t="n">
+      <c r="S543" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T543" t="inlineStr">
@@ -57901,7 +58041,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S544" t="n">
+      <c r="S544" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T544" t="inlineStr">
@@ -58005,7 +58145,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S545" t="n">
+      <c r="S545" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T545" t="inlineStr">
@@ -58109,7 +58249,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S546" t="n">
+      <c r="S546" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T546" t="inlineStr">
@@ -58208,7 +58348,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S547" t="n">
+      <c r="S547" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T547" t="inlineStr">
@@ -58307,7 +58447,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S548" t="n">
+      <c r="S548" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T548" t="inlineStr">
@@ -58411,7 +58551,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S549" t="n">
+      <c r="S549" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T549" t="inlineStr">
@@ -58520,7 +58660,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S550" t="n">
+      <c r="S550" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T550" t="inlineStr">
@@ -58624,7 +58764,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S551" t="n">
+      <c r="S551" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T551" t="inlineStr">
@@ -58728,7 +58868,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S552" t="n">
+      <c r="S552" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T552" t="inlineStr">
@@ -58827,7 +58967,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S553" t="n">
+      <c r="S553" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T553" t="inlineStr">
@@ -58874,7 +59014,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Riet- en beetwortelsuiker, geraffineerd (Prodcom 108112)</t>
+          <t>Riet- en beetwortelsuiker, geraffineerd - productie van het Vlaamse bedrijf (sites in Vlaanderen en Wallonie) (Prodcom 108112)</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -58931,7 +59071,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S554" t="n">
+      <c r="S554" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T554" t="inlineStr">
@@ -58941,7 +59081,7 @@
       </c>
       <c r="U554" t="inlineStr">
         <is>
-          <t>hoofdstroom NACE 10.81; Vlaams aandeel 69% (exportproxy); mengt riet- en bietsuiker</t>
+          <t>hoofdstroom NACE 10.81; Vlaams aandeel 69% (exportproxy); mengt riet- en bietsuiker; de bron definieert dit op folio 118 als 'de productiehoeveelheid van het Vlaamse bedrijf', waarvan de sites over Vlaanderen en Wallonie verspreid liggen; het is dus GEEN Vlaams grondgebiedcijfer, ook al staat het in de kolom 'Productie Vlaanderen'</t>
         </is>
       </c>
       <c r="V554" t="inlineStr">
@@ -58951,7 +59091,7 @@
       </c>
       <c r="W554" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X554" t="inlineStr">
@@ -58961,7 +59101,7 @@
       </c>
       <c r="Z554" t="inlineStr">
         <is>
-          <t>ook in tekst folio 118; variant: de bron citeert daar ook FoodIndustry (2020) met 650.000 ton</t>
+          <t>ook in tekst folio 118; hiervan is 275.044 t op Vlaams grondgebied geproduceerd - zie C-572, dat het Vlaamse cijfer is; variant: FoodIndustry (2020) schat dezelfde bedrijfsproductie op 650.000 t - zie C-573</t>
         </is>
       </c>
     </row>
@@ -59040,7 +59180,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S555" t="n">
+      <c r="S555" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T555" t="inlineStr">
@@ -59149,7 +59289,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S556" t="n">
+      <c r="S556" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T556" t="inlineStr">
@@ -59263,7 +59403,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S557" t="n">
+      <c r="S557" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T557" t="inlineStr">
@@ -59372,7 +59512,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S558" t="n">
+      <c r="S558" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T558" t="inlineStr">
@@ -59471,7 +59611,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S559" t="n">
+      <c r="S559" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T559" t="inlineStr">
@@ -59570,7 +59710,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S560" t="n">
+      <c r="S560" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T560" t="inlineStr">
@@ -59679,7 +59819,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S561" t="n">
+      <c r="S561" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T561" t="inlineStr">
@@ -59778,7 +59918,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S562" t="n">
+      <c r="S562" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T562" t="inlineStr">
@@ -59877,7 +60017,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S563" t="n">
+      <c r="S563" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T563" t="inlineStr">
@@ -59976,7 +60116,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S564" t="n">
+      <c r="S564" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T564" t="inlineStr">
@@ -60075,7 +60215,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S565" t="n">
+      <c r="S565" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T565" t="inlineStr">
@@ -60174,7 +60314,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S566" t="n">
+      <c r="S566" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T566" t="inlineStr">
@@ -60273,7 +60413,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S567" t="n">
+      <c r="S567" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T567" t="inlineStr">
@@ -60372,7 +60512,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S568" t="n">
+      <c r="S568" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T568" t="inlineStr">
@@ -60476,7 +60616,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S569" t="n">
+      <c r="S569" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T569" t="inlineStr">
@@ -60575,7 +60715,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S570" t="n">
+      <c r="S570" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T570" t="inlineStr">
@@ -60674,7 +60814,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S571" t="n">
+      <c r="S571" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T571" t="inlineStr">
@@ -60773,7 +60913,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S572" t="n">
+      <c r="S572" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T572" t="inlineStr">
@@ -60820,7 +60960,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Suikerproductie op Vlaamse productiesites (grondgebiedbasis)</t>
+          <t>Suikerproductie op Vlaams grondgebied (35% van de Belgische productie) - het Vlaamse cijfer</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -60877,7 +61017,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S573" t="n">
+      <c r="S573" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T573" t="inlineStr">
@@ -60907,7 +61047,7 @@
       </c>
       <c r="Z573" t="inlineStr">
         <is>
-          <t>parallelle afbakening naast de 538.889 ton van Tabel 85 (exportproxy 69%) - niet optellen</t>
+          <t>deelverzameling van de 538.889 t bedrijfsproductie in C-553 (Belgie), niet een alternatieve meting daarvan - niet optellen</t>
         </is>
       </c>
     </row>
@@ -60929,7 +61069,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Suikerproductie Vlaanderen volgens FoodIndustry (2020)</t>
+          <t>Suikerproductie van het Vlaamse bedrijf volgens FoodIndustry (2020) (sites in Vlaanderen en Wallonie)</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -60986,7 +61126,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S574" t="n">
+      <c r="S574" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T574" t="inlineStr">
@@ -60996,7 +61136,7 @@
       </c>
       <c r="U574" t="inlineStr">
         <is>
-          <t>schatting van een derde bron die de bron zelf naast haar eigen 538.889 ton plaatst</t>
+          <t>schatting van een derde bron die de bron zelf naast haar eigen 538.889 ton plaatst; betreft dezelfde bedrijfsafbakening als C-553 en dus geen Vlaams grondgebiedcijfer</t>
         </is>
       </c>
       <c r="V574" t="inlineStr">
@@ -61006,7 +61146,7 @@
       </c>
       <c r="W574" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X574" t="inlineStr">
@@ -61016,7 +61156,7 @@
       </c>
       <c r="Z574" t="inlineStr">
         <is>
-          <t>variant van de 538.889 ton uit Tabel 85 (folio 260)</t>
+          <t>variant van de 538.889 t in C-553 (zelfde bedrijfsafbakening); het Vlaamse grondgebiedcijfer is C-572</t>
         </is>
       </c>
     </row>
@@ -61095,7 +61235,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S575" t="n">
+      <c r="S575" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T575" t="inlineStr">
@@ -61214,7 +61354,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S576" t="n">
+      <c r="S576" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T576" t="inlineStr">
@@ -61318,7 +61458,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S577" t="n">
+      <c r="S577" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T577" t="inlineStr">
@@ -61422,7 +61562,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S578" t="n">
+      <c r="S578" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T578" t="inlineStr">
@@ -61526,7 +61666,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S579" t="n">
+      <c r="S579" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T579" t="inlineStr">
@@ -61625,7 +61765,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S580" t="n">
+      <c r="S580" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T580" t="inlineStr">
@@ -61724,7 +61864,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S581" t="n">
+      <c r="S581" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T581" t="inlineStr">
@@ -61823,7 +61963,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S582" t="n">
+      <c r="S582" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T582" t="inlineStr">
@@ -61922,7 +62062,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S583" t="n">
+      <c r="S583" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T583" t="inlineStr">
@@ -62021,7 +62161,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S584" t="n">
+      <c r="S584" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T584" t="inlineStr">
@@ -62125,7 +62265,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S585" t="n">
+      <c r="S585" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T585" t="inlineStr">
@@ -62224,7 +62364,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S586" t="n">
+      <c r="S586" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T586" t="inlineStr">
@@ -62328,7 +62468,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S587" t="n">
+      <c r="S587" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T587" t="inlineStr">
@@ -62338,7 +62478,7 @@
       </c>
       <c r="U587" t="inlineStr">
         <is>
-          <t>de federatie vertegenwoordigt 95% van het Belgische productievolume; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106)</t>
+          <t>de federatie vertegenwoordigt 95% van het Belgische productievolume; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V587" t="inlineStr">
@@ -62358,7 +62498,7 @@
       </c>
       <c r="Z587" t="inlineStr">
         <is>
-          <t>afgerond '23,6 miljoen hl' in tekst folio 122; variant van de 22.465.944 hl (Statbel) in dezelfde tabel</t>
+          <t>afgerond '23,6 miljoen hl' in tekst folio 122; variant van de 22.465.944 hl (Statbel) in dezelfde tabel; zelfde geval als C-393 in S091, dat de reviewer heeft afgewezen: een Belgisch cijfer waarvoor ook een Vlaams cijfer bestaat (C-588)</t>
         </is>
       </c>
     </row>
@@ -62437,7 +62577,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S588" t="n">
+      <c r="S588" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T588" t="inlineStr">
@@ -62447,7 +62587,7 @@
       </c>
       <c r="U588" t="inlineStr">
         <is>
-          <t>Statbel-cijfer; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106)</t>
+          <t>Statbel-cijfer; omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V588" t="inlineStr">
@@ -62467,7 +62607,7 @@
       </c>
       <c r="Z588" t="inlineStr">
         <is>
-          <t>afgerond '22,5 miljoen hl' in tekst folio 122; ook in Tabel 87 (folio 264); variant van de 23.572.769 hl van Belgische Brouwers</t>
+          <t>afgerond '22,5 miljoen hl' in tekst folio 122; ook in Tabel 87 (folio 264); variant van de 23.572.769 hl van Belgische Brouwers; zelfde geval als C-394 in S091, dat de reviewer heeft afgewezen: een Belgisch cijfer waarvoor ook een Vlaams cijfer bestaat (C-588)</t>
         </is>
       </c>
     </row>
@@ -62546,7 +62686,7 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="S589" t="n">
+      <c r="S589" s="24" t="n">
         <v>0.105</v>
       </c>
       <c r="T589" t="inlineStr">
@@ -62556,7 +62696,7 @@
       </c>
       <c r="U589" t="inlineStr">
         <is>
-          <t>Vlaams aandeel 73% (exportratio); omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106)</t>
+          <t>Vlaams aandeel 73% (exportratio); omrekening met het door de bron opgegeven soortelijk gewicht van 1.050 g/l (folio 106) Omrekening: 1 hl = 100 l x 1.050 g/l = 0,105 t (dichtheid door de bron opgegeven).</t>
         </is>
       </c>
       <c r="V589" t="inlineStr">
@@ -62655,7 +62795,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S590" t="n">
+      <c r="S590" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T590" t="inlineStr">
@@ -62764,7 +62904,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S591" t="n">
+      <c r="S591" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T591" t="inlineStr">
@@ -62878,7 +63018,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S592" t="n">
+      <c r="S592" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T592" t="inlineStr">
@@ -62987,7 +63127,7 @@
           <t>ton</t>
         </is>
       </c>
-      <c r="S593" t="n">
+      <c r="S593" s="24" t="n">
         <v>1</v>
       </c>
       <c r="T593" t="inlineStr">
@@ -63027,12 +63167,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y109"/>
+  <dimension ref="A1:Y398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="7.26953125" customWidth="1" min="1" max="1"/>
+    <col hidden="1" width="7.26953125" customWidth="1" min="1" max="1"/>
+    <col hidden="1" width="8.7265625" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="51.6328125" customWidth="1" min="4" max="4"/>
+    <col width="72.54296875" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="22.6328125" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
@@ -63043,14 +63184,14 @@
     <col width="29.7265625" customWidth="1" min="12" max="12"/>
     <col width="11.81640625" customWidth="1" min="13" max="13"/>
     <col width="0.1796875" customWidth="1" min="14" max="14"/>
-    <col width="7.36328125" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="14.08984375" customWidth="1" min="15" max="15"/>
+    <col width="15.453125" customWidth="1" min="16" max="16"/>
     <col width="13.26953125" customWidth="1" min="17" max="17"/>
     <col width="10.36328125" customWidth="1" min="18" max="18"/>
-    <col width="6.54296875" customWidth="1" min="19" max="19"/>
+    <col width="12.54296875" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="22.08984375" customWidth="1" min="21" max="21"/>
-    <col width="8.54296875" customWidth="1" min="22" max="22"/>
+    <col width="38.36328125" customWidth="1" min="21" max="21"/>
+    <col width="27.26953125" customWidth="1" min="22" max="22"/>
     <col width="11.81640625" customWidth="1" style="7" min="23" max="23"/>
     <col width="11.90625" customWidth="1" min="24" max="24"/>
     <col width="11.54296875" customWidth="1" min="25" max="25"/>
@@ -63265,9 +63406,9 @@
           <t>Passes all 3 tests. VERIFIED BY READING: covers the animal by-product processing sector (~860 kt processed 2021 -&gt; 476 kt derived products) and used frying fats/oils, alongside open-ruimte/wood. My original 'partly agri-food' rating was wrong.</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>EXTRACTED - source read, claims taken</t>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W2" s="11" t="inlineStr">
@@ -63471,9 +63612,9 @@
           <t>Passes all 3. Confirmed to carry NAMED stream tonnages (bietenpulp+melasse 458 kt, bostel 80 kt, gries/zemelen/DDGS 646 kt), not just sector aggregates.</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>NOT EXTRACTED (was stale metadata from the superseded root-level corpus; corrected 2026-08-16)</t>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W4" s="7" t="inlineStr">
@@ -63574,9 +63715,9 @@
           <t>Passes all 3. Separate reference year (2019/20). Cited as source A in the ILVO hub tables.</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>NOT EXTRACTED (was stale metadata from the superseded root-level corpus; corrected 2026-08-16)</t>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W5" s="7" t="inlineStr">
@@ -63778,9 +63919,9 @@
           <t>Passes all 3. ILVO Mededeling nr 165, official URL verified. One of the three studies the whole Flemish field rests on. CAVEATS: data are 2010-2012; processing-industry figures are BELGIUM not Flanders; no retail or catering coverage; reports WET tonnages.</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>EXTRACTED - source read, claims taken</t>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W7" s="7" t="inlineStr">
@@ -63881,9 +64022,9 @@
           <t>Passes all 3. Title now confirmed exactly: 'Monitoring van voedselreststromen en voedselverliezen in de Vlaamse tuinbouw' (ILVO + Vlaamse Overheid, 2018, ref. yr 2015). Cited as source C throughout the ILVO hub tables. STILL NO DIRECT URL - the main outstanding gap in the register.</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>PARTIALLY EXTRACTED - claims taken, source not exhausted</t>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W8" s="7" t="inlineStr">
@@ -64293,9 +64434,9 @@
           <t>Passes all 3. Newest Marktanalyse edition (published 2025-03), direct URL verified. Should be read before the 2022 edition.</t>
         </is>
       </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>EXTRACTED - source read, claims taken</t>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W12" s="7" t="inlineStr">
@@ -64396,9 +64537,9 @@
           <t>Passes all 3. READ IN FULL. Tables 2-5 are the single richest per-stream table set found, each cell attributed to one of 4 primary sources. Not an independent measurement - a consolidation - but that is exactly its value.</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>EXTRACTED - source read, claims taken</t>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
       <c r="W13" s="7" t="inlineStr">
@@ -64698,7 +64839,7 @@
           <t>Passes all 3. Separate reference year (2021/2022).</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>EXTRACTED - source read, claims taken</t>
         </is>
@@ -65590,9 +65731,9 @@
           <t>Passes 2 and 3; test 1 at BELGIUM level. A real three-year study of 5 Belgian retailers 2015-2018: 75,000 t supermarket food waste in 2018, 14.4% donated, ~60,000 t sorted organic + ~4,000 t unsorted, plus a destination split. Upgrades and replaces S036.</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>PARTIALLY EXTRACTED - claims taken, source not exhausted</t>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>NOT EXTRACTED</t>
         </is>
       </c>
     </row>
@@ -72167,28 +72308,49 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
     <row r="109">
       <c r="D109" t="inlineStr">
         <is>
           <t>AGGREGAAT - totale voedselverliezen voedingsretail en grootdistributie</t>
         </is>
       </c>
+    </row>
+    <row r="115" customFormat="1" s="17">
+      <c r="W115" s="18" t="n"/>
+    </row>
+    <row r="148">
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" customFormat="1" s="17">
+      <c r="W215" s="18" t="n"/>
+    </row>
+    <row r="398" customFormat="1" s="17">
+      <c r="W398" s="18" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:V92">

--- a/database/register/BIOLOOP_streams_and_sources.xlsx
+++ b/database/register/BIOLOOP_streams_and_sources.xlsx
@@ -28770,7 +28770,7 @@
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>aanlanding door Belgische vissersvaartuigen; 99% hoofdstromen</t>
+          <t>aanlanding door Belgische vissersvaartuigen; 99% hoofdstromen Bron schrijft "Belgische vissersvaartuigen"; alle Belgische vissershavens liggen in Vlaanderen, zodat het nationale en het Vlaamse cijfer samenvallen (gesanctioneerde uitzondering op de geography-regel).</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>aangeland door Belgische vissersvaartuigen</t>
+          <t>aangeland door Belgische vissersvaartuigen Bron schrijft "Belgische vissersvaartuigen"; alle Belgische vissershavens liggen in Vlaanderen, zodat het nationale en het Vlaamse cijfer samenvallen (gesanctioneerde uitzondering op de geography-regel).</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>aangeland door Belgische vissersvaartuigen</t>
+          <t>aangeland door Belgische vissersvaartuigen Bron schrijft "Belgische vissersvaartuigen"; alle Belgische vissershavens liggen in Vlaanderen, zodat het nationale en het Vlaamse cijfer samenvallen (gesanctioneerde uitzondering op de geography-regel).</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>aangeland door Belgische vissersvaartuigen</t>
+          <t>aangeland door Belgische vissersvaartuigen Bron schrijft "Belgische vissersvaartuigen"; alle Belgische vissershavens liggen in Vlaanderen, zodat het nationale en het Vlaamse cijfer samenvallen (gesanctioneerde uitzondering op de geography-regel).</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie hoofdstromen</t>
+          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie hoofdstromen (Belgisch FEDIOL-cijfer, door de bron in de Vlaamse tabel gezet)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>geconsolideerde tabel voedingssector, kolom productie/hoofd; overgenomen uit Tabel 32 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd</t>
+          <t>geconsolideerde tabel voedingssector, kolom productie/hoofd; overgenomen uit Tabel 32 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd De tabeltitel zegt "Vlaamse voedingssector", maar de bron stelt zelf dat voor NACE 10.4 de FEDIOL-cijfers voor Belgie gebruikt zijn; de materiele dekking is dus Belgisch en geography staat daarom op Belgie.</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
@@ -29870,12 +29870,17 @@
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X280" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>zelfde getal en zelfde dekking als C-329 (Tabel 32, FEDIOL Belgie, p.91) - dit is een herhaling van dat cijfer in de samenvattende tabel, geen onafhankelijke meting; de reviewer kan een van beide rijen laten vervallen</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29902,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie nevenstromen en productieresiduen</t>
+          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie nevenstromen en productieresiduen (Belgisch FEDIOL-cijfer, door de bron in de Vlaamse tabel gezet)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -29959,7 +29964,7 @@
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>geconsolideerde tabel voedingssector, kolom productie/nev-res; overgenomen uit Tabel 33 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd</t>
+          <t>geconsolideerde tabel voedingssector, kolom productie/nev-res; overgenomen uit Tabel 33 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd De tabeltitel zegt "Vlaamse voedingssector", maar de bron stelt zelf dat voor NACE 10.4 de FEDIOL-cijfers voor Belgie gebruikt zijn; de materiele dekking is dus Belgisch en geography staat daarom op Belgie.</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
@@ -29969,12 +29974,17 @@
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>zelfde getal en zelfde dekking als C-335 (Tabel 33, FEDIOL Belgie, p.91) - dit is een herhaling van dat cijfer in de samenvattende tabel, geen onafhankelijke meting; de reviewer kan een van beide rijen laten vervallen</t>
         </is>
       </c>
     </row>
@@ -35235,7 +35245,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>hetzelfde getal staat als Vlaams cijfer in Tabel 26 (p.76) - zie de anomalienota</t>
+          <t>hetzelfde getal staat in Tabel 26 (p.76) in de kolom van de Vlaamse voedingssector - zie C-279, dat nu eveneens geography Belgie draagt; '504 kton voor Belgie' ook in tekst p.90 en p.4</t>
         </is>
       </c>
     </row>
@@ -35884,7 +35894,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>hetzelfde getal staat als Vlaams cijfer in Tabel 26 (p.76) - zie de anomalienota; '1.149 kton voor Belgie' ook in tekst p.4</t>
+          <t>hetzelfde getal staat in Tabel 26 (p.76) in de kolom van de Vlaamse voedingssector - zie C-280, dat nu eveneens geography Belgie draagt; '1.149 kton voor Belgie' ook in tekst p.4</t>
         </is>
       </c>
     </row>
@@ -49563,7 +49573,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie hoofdstromen</t>
+          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie hoofdstromen (Belgisch FEDIOL-cijfer, door de bron in de Vlaamse tabel gezet)</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -49625,7 +49635,7 @@
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>geconsolideerde tabel verwerkingssectoren, kolom productie/hoofd; overgenomen uit Tabel 30 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd</t>
+          <t>geconsolideerde tabel verwerkingssectoren, kolom productie/hoofd; overgenomen uit Tabel 30 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd De tabeltitel zegt "Vlaamse voedingssector", maar de bron stelt zelf dat voor NACE 10.4 de FEDIOL-cijfers voor Belgie gebruikt zijn; de materiele dekking is dus Belgisch en geography staat daarom op Belgie.</t>
         </is>
       </c>
       <c r="V465" t="inlineStr">
@@ -49635,12 +49645,17 @@
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X465" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t>zelfde getal en zelfde dekking als C-518 (Tabel 30, FEDIOL Belgie, folio 115) - een herhaling in de samenvattende tabel, geen onafhankelijke meting; de reviewer kan een van beide rijen laten vervallen</t>
         </is>
       </c>
     </row>
@@ -49662,7 +49677,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie nevenstromen en productieresiduen</t>
+          <t>AGGREGAAT - Vervaardiging van plantaardige en dierlijke olien en vetten, productie nevenstromen en productieresiduen (Belgisch FEDIOL-cijfer, door de bron in de Vlaamse tabel gezet)</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -49724,7 +49739,7 @@
       </c>
       <c r="U466" t="inlineStr">
         <is>
-          <t>geconsolideerde tabel verwerkingssectoren, kolom productie/nev-res; overgenomen uit Tabel 31 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd</t>
+          <t>geconsolideerde tabel verwerkingssectoren, kolom productie/nev-res; overgenomen uit Tabel 31 (FEDIOL, Belgie) maar hier als Vlaams cijfer gepresenteerd De tabeltitel zegt "Vlaamse voedingssector", maar de bron stelt zelf dat voor NACE 10.4 de FEDIOL-cijfers voor Belgie gebruikt zijn; de materiele dekking is dus Belgisch en geography staat daarom op Belgie.</t>
         </is>
       </c>
       <c r="V466" t="inlineStr">
@@ -49734,12 +49749,17 @@
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>Vlaanderen</t>
+          <t>Belgie</t>
         </is>
       </c>
       <c r="X466" t="inlineStr">
         <is>
           <t>read in PDF</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t>zelfde getal en zelfde dekking als C-524 (Tabel 31, FEDIOL Belgie, folio 116) - een herhaling in de samenvattende tabel, geen onafhankelijke meting; de reviewer kan een van beide rijen laten vervallen</t>
         </is>
       </c>
     </row>
@@ -55406,7 +55426,7 @@
       </c>
       <c r="Z519" t="inlineStr">
         <is>
-          <t>hetzelfde getal staat als Vlaams cijfer in Tabel 28 (folio 108) - zie de anomalienota</t>
+          <t>hetzelfde getal staat in Tabel 28 (folio 108) in de kolom van de Vlaamse verwerkingssectoren - zie C-464, dat nu eveneens geography Belgie draagt</t>
         </is>
       </c>
     </row>
@@ -56055,7 +56075,7 @@
       </c>
       <c r="Z525" t="inlineStr">
         <is>
-          <t>hetzelfde getal staat als Vlaams cijfer in Tabel 28 (folio 108) - zie de anomalienota; '1.376 kton voor Belgie' ook in tekst folio 4</t>
+          <t>hetzelfde getal staat in Tabel 28 (folio 108) in de kolom van de Vlaamse verwerkingssectoren - zie C-465, dat nu eveneens geography Belgie draagt; '1.376 kton voor Belgie' ook in tekst folio 4</t>
         </is>
       </c>
     </row>
